--- a/codelists/ischaemic_heart_disease_raw.xlsx
+++ b/codelists/ischaemic_heart_disease_raw.xlsx
@@ -6074,7 +6074,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>299800012</t>
+          <t>299804015</t>
         </is>
       </c>
       <c r="B118" s="1" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>G34y</t>
+          <t>G34yz</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>G34y.00</t>
+          <t>G34yz00</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Other specified chronic ischaemic heart disease</t>
+          <t>Other specified chronic ischaemic heart disease NOS</t>
         </is>
       </c>
       <c r="H118" s="1" t="n">
@@ -6125,7 +6125,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>299804015</t>
+          <t>299800012</t>
         </is>
       </c>
       <c r="B119" s="1" t="n">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>G34yz</t>
+          <t>G34y</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>G34yz00</t>
+          <t>G34y.00</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Other specified chronic ischaemic heart disease NOS</t>
+          <t>Other specified chronic ischaemic heart disease</t>
         </is>
       </c>
       <c r="H119" s="1" t="n">

--- a/codelists/ischaemic_heart_disease_raw.xlsx
+++ b/codelists/ischaemic_heart_disease_raw.xlsx
@@ -410,14 +410,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O213"/>
+  <dimension ref="A1:O217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.48" customWidth="1" min="1" max="1"/>
     <col width="12.88" customWidth="1" min="2" max="2"/>
     <col width="17.48" customWidth="1" min="3" max="3"/>
     <col width="16.56" customWidth="1" min="4" max="4"/>
-    <col width="18.4" customWidth="1" min="5" max="5"/>
+    <col width="17.48" customWidth="1" min="5" max="5"/>
     <col width="21.16" customWidth="1" min="6" max="6"/>
     <col width="153.64" customWidth="1" min="7" max="7"/>
     <col width="4.600000000000001" customWidth="1" min="8" max="8"/>
@@ -2058,7 +2058,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>299782012</t>
+          <t>634811000006114</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -2066,34 +2066,34 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>G3400</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>G340000</t>
+          <t>3221.00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>194842008</t>
+          <t>164862008</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>299782012</t>
+          <t>1205557014</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Single coronary vessel disease</t>
+          <t>ECG no myocardial ischaemia</t>
         </is>
       </c>
       <c r="H34" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I34" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="1" t="n"/>
       <c r="K34" s="1" t="n"/>
@@ -2105,7 +2105,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>406961000000113</t>
+          <t>299782012</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -2113,34 +2113,34 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>9Ob9</t>
+          <t>G3400</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9Ob9.00</t>
+          <t>G340000</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>248461000000107</t>
+          <t>194842008</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>406961000000113</t>
+          <t>299782012</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Coronary heart disease monitoring telephone invite</t>
+          <t>Single coronary vessel disease</t>
         </is>
       </c>
       <c r="H35" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="1" t="n"/>
       <c r="K35" s="1" t="n"/>
@@ -2152,31 +2152,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8459551000006115</t>
+          <t>406961000000113</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>^ESCTCO845955</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>9Ob9</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>9Ob9.00</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1083121000000102</t>
+          <t>248461000000107</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2714171000000118</t>
+          <t>406961000000113</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Coronary heart disease monitoring invitation</t>
+          <t>Coronary heart disease monitoring telephone invite</t>
         </is>
       </c>
       <c r="H36" s="1" t="n">
@@ -2195,7 +2199,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>264494013</t>
+          <t>8459551000006115</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
@@ -2203,27 +2207,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>662K1</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>662K100</t>
-        </is>
-      </c>
+          <t>^ESCTCO845955</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>170595000</t>
+          <t>1083121000000102</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>264494013</t>
+          <t>2714171000000118</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Angina control - poor</t>
+          <t>Coronary heart disease monitoring invitation</t>
         </is>
       </c>
       <c r="H37" s="1" t="n">
@@ -2242,7 +2242,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>264496010</t>
+          <t>264494013</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
@@ -2250,27 +2250,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>662K3</t>
+          <t>662K1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>662K300</t>
+          <t>662K100</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>170597008</t>
+          <t>170595000</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>264496010</t>
+          <t>264494013</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Angina control - worsening</t>
+          <t>Angina control - poor</t>
         </is>
       </c>
       <c r="H38" s="1" t="n">
@@ -2289,7 +2289,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>299783019</t>
+          <t>264496010</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
@@ -2297,34 +2297,34 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>G3401</t>
+          <t>662K3</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>G340100</t>
+          <t>662K300</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>194843003</t>
+          <t>170597008</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>299783019</t>
+          <t>264496010</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Double coronary vessel disease</t>
+          <t>Angina control - worsening</t>
         </is>
       </c>
       <c r="H39" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="1" t="n"/>
       <c r="K39" s="1" t="n"/>
@@ -2336,7 +2336,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>314321000000119</t>
+          <t>299783019</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
@@ -2344,34 +2344,34 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1J61</t>
+          <t>G3401</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1J61.00</t>
+          <t>G340100</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>205011000000103</t>
+          <t>194843003</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>314321000000119</t>
+          <t>299783019</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Suspected ischaemic heart disease</t>
+          <t>Double coronary vessel disease</t>
         </is>
       </c>
       <c r="H40" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I40" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="1" t="n"/>
       <c r="K40" s="1" t="n"/>
@@ -2383,7 +2383,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>442204010</t>
+          <t>314321000000119</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -2391,27 +2391,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>G33z3</t>
+          <t>1J61</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>G33z300</t>
+          <t>1J61.00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>300995000</t>
+          <t>205011000000103</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>442204010</t>
+          <t>314321000000119</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Angina on effort</t>
+          <t>Suspected ischaemic heart disease</t>
         </is>
       </c>
       <c r="H41" s="1" t="n">
@@ -2423,18 +2423,14 @@
       <c r="J41" s="1" t="n"/>
       <c r="K41" s="1" t="n"/>
       <c r="L41" s="1" t="n"/>
-      <c r="M41" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M41" s="1" t="n"/>
       <c r="N41" s="1" t="n"/>
-      <c r="O41" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O41" s="1" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1780442013</t>
+          <t>442204010</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -2442,27 +2438,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>9Ob0</t>
+          <t>G33z3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9Ob0.00</t>
+          <t>G33z300</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>401248001</t>
+          <t>300995000</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1780442013</t>
+          <t>442204010</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Attends coronary heart disease monitoring</t>
+          <t>Angina on effort</t>
         </is>
       </c>
       <c r="H42" s="1" t="n">
@@ -2474,14 +2470,18 @@
       <c r="J42" s="1" t="n"/>
       <c r="K42" s="1" t="n"/>
       <c r="L42" s="1" t="n"/>
-      <c r="M42" s="1" t="n"/>
+      <c r="M42" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N42" s="1" t="n"/>
-      <c r="O42" s="1" t="n"/>
+      <c r="O42" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13823711000006118</t>
+          <t>1780442013</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -2489,23 +2489,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>^ESCT1382371</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>9Ob0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>9Ob0.00</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>401250009</t>
+          <t>401248001</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3767916014</t>
+          <t>1780442013</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Coronary heart disease monitoring first letter</t>
+          <t>Attends coronary heart disease monitoring</t>
         </is>
       </c>
       <c r="H43" s="1" t="n">
@@ -2524,7 +2528,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>299776014</t>
+          <t>13823711000006118</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -2532,27 +2536,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>G34</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>G34..00</t>
-        </is>
-      </c>
+          <t>^ESCT1382371</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>413838009</t>
+          <t>401250009</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2534672016</t>
+          <t>3767916014</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chronic ischaemic heart disease</t>
+          <t>Coronary heart disease monitoring first letter</t>
         </is>
       </c>
       <c r="H44" s="1" t="n">
@@ -2564,18 +2564,14 @@
       <c r="J44" s="1" t="n"/>
       <c r="K44" s="1" t="n"/>
       <c r="L44" s="1" t="n"/>
-      <c r="M44" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M44" s="1" t="n"/>
       <c r="N44" s="1" t="n"/>
-      <c r="O44" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O44" s="1" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>496981000006113</t>
+          <t>299776014</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
@@ -2583,46 +2579,50 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>G70</t>
+          <t>G34</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>G70..00</t>
+          <t>G34..00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>72092001</t>
+          <t>413838009</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>119795011</t>
+          <t>2534672016</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Arteriosclerotic vascular disease</t>
+          <t>Chronic ischaemic heart disease</t>
         </is>
       </c>
       <c r="H45" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I45" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="1" t="n"/>
       <c r="K45" s="1" t="n"/>
       <c r="L45" s="1" t="n"/>
-      <c r="M45" s="1" t="n"/>
+      <c r="M45" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N45" s="1" t="n"/>
-      <c r="O45" s="1" t="n"/>
+      <c r="O45" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>908791000006113</t>
+          <t>496981000006113</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
@@ -2630,30 +2630,34 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HNG0601</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>G70</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>G70..00</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>908791000006109</t>
+          <t>72092001</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>908791000006113</t>
+          <t>119795011</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[RFC] Coronary heart disease</t>
+          <t>Arteriosclerotic vascular disease</t>
         </is>
       </c>
       <c r="H46" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I46" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" s="1" t="n"/>
       <c r="K46" s="1" t="n"/>
@@ -2665,31 +2669,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>12626301000006112</t>
+          <t>908791000006113</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>^ESCT1262630</t>
+          <t>HNG0601</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1110881000000106</t>
+          <t>908791000006109</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2779741000000117</t>
+          <t>908791000006113</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>QOF (Quality and Outcomes Framework) secondary prevention of coronary heart disease quality indicator-related care invitation</t>
+          <t>[RFC] Coronary heart disease</t>
         </is>
       </c>
       <c r="H47" s="1" t="n">
@@ -2708,7 +2712,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>264495014</t>
+          <t>12626301000006112</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
@@ -2716,27 +2720,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>662K2</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>662K200</t>
-        </is>
-      </c>
+          <t>^ESCT1262630</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>170596004</t>
+          <t>1110881000000106</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>264495014</t>
+          <t>2779741000000117</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Angina control - improving</t>
+          <t>QOF (Quality and Outcomes Framework) secondary prevention of coronary heart disease quality indicator-related care invitation</t>
         </is>
       </c>
       <c r="H48" s="1" t="n">
@@ -2755,7 +2755,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>299745015</t>
+          <t>264495014</t>
         </is>
       </c>
       <c r="B49" s="1" t="n">
@@ -2763,54 +2763,46 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>G31y0</t>
+          <t>662K2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>G31y000</t>
+          <t>662K200</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>194823009</t>
+          <t>170596004</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>299745015</t>
+          <t>264495014</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Acute coronary insufficiency</t>
+          <t>Angina control - improving</t>
         </is>
       </c>
       <c r="H49" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I49" s="1" t="n"/>
-      <c r="J49" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K49" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M49" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="I49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1" t="n"/>
+      <c r="K49" s="1" t="n"/>
+      <c r="L49" s="1" t="n"/>
+      <c r="M49" s="1" t="n"/>
       <c r="N49" s="1" t="n"/>
-      <c r="O49" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O49" s="1" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>8079871000006116</t>
+          <t>299745015</t>
         </is>
       </c>
       <c r="B50" s="1" t="n">
@@ -2818,23 +2810,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>^ESCTCO807987</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>G31y0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>G31y000</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>248461000000107</t>
+          <t>194823009</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1153801000000119</t>
+          <t>299745015</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Coronary heart disease monitoring telephone invitation</t>
+          <t>Acute coronary insufficiency</t>
         </is>
       </c>
       <c r="H50" s="1" t="n">
@@ -2843,17 +2839,27 @@
       <c r="I50" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="1" t="n"/>
-      <c r="K50" s="1" t="n"/>
-      <c r="L50" s="1" t="n"/>
-      <c r="M50" s="1" t="n"/>
+      <c r="J50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N50" s="1" t="n"/>
-      <c r="O50" s="1" t="n"/>
+      <c r="O50" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1780517019</t>
+          <t>8079871000006116</t>
         </is>
       </c>
       <c r="B51" s="1" t="n">
@@ -2861,27 +2867,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>9Ob2</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>9Ob2.00</t>
-        </is>
-      </c>
+          <t>^ESCTCO807987</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>401331007</t>
+          <t>248461000000107</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1780517019</t>
+          <t>1153801000000119</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Coronary heart disease monitoring default</t>
+          <t>Coronary heart disease monitoring telephone invitation</t>
         </is>
       </c>
       <c r="H51" s="1" t="n">
@@ -2900,7 +2902,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>299741012</t>
+          <t>1780517019</t>
         </is>
       </c>
       <c r="B52" s="1" t="n">
@@ -2908,27 +2910,27 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>G311z</t>
+          <t>9Ob2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>G311z00</t>
+          <t>9Ob2.00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>4557003</t>
+          <t>401331007</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>7844010</t>
+          <t>1780517019</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Preinfarction syndrome</t>
+          <t>Coronary heart disease monitoring default</t>
         </is>
       </c>
       <c r="H52" s="1" t="n">
@@ -2937,29 +2939,17 @@
       <c r="I52" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N52" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="J52" s="1" t="n"/>
+      <c r="K52" s="1" t="n"/>
+      <c r="L52" s="1" t="n"/>
+      <c r="M52" s="1" t="n"/>
+      <c r="N52" s="1" t="n"/>
+      <c r="O52" s="1" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1774801000000114</t>
+          <t>299741012</t>
         </is>
       </c>
       <c r="B53" s="1" t="n">
@@ -2967,27 +2957,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>8CMP</t>
+          <t>G311z</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8CMP.00</t>
+          <t>G311z00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>736368003</t>
+          <t>4557003</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>3517259010</t>
+          <t>7844010</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Coronary heart disease care plan</t>
+          <t>Preinfarction syndrome</t>
         </is>
       </c>
       <c r="H53" s="1" t="n">
@@ -2996,45 +2986,57 @@
       <c r="I53" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="1" t="n"/>
-      <c r="K53" s="1" t="n"/>
-      <c r="L53" s="1" t="n"/>
-      <c r="M53" s="1" t="n"/>
-      <c r="N53" s="1" t="n"/>
-      <c r="O53" s="1" t="n"/>
+      <c r="J53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>461307013</t>
+          <t>1774801000000114</t>
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ZV7B0</t>
+          <t>8CMP</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ZV7B000</t>
+          <t>8CMP.00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>171223006</t>
+          <t>736368003</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>265320019</t>
+          <t>3517259010</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ischemic heart disease screening</t>
+          <t>Coronary heart disease care plan</t>
         </is>
       </c>
       <c r="H54" s="1" t="n">
@@ -3053,7 +3055,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7847015</t>
+          <t>461307013</t>
         </is>
       </c>
       <c r="B55" s="1" t="n">
@@ -3061,27 +3063,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>G311-1</t>
+          <t>ZV7B0</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>G311.11</t>
+          <t>ZV7B000</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4557003</t>
+          <t>171223006</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>7847015</t>
+          <t>265320019</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crescendo angina</t>
+          <t>Ischemic heart disease screening</t>
         </is>
       </c>
       <c r="H55" s="1" t="n">
@@ -3090,42 +3092,30 @@
       <c r="I55" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="J55" s="1" t="n"/>
+      <c r="K55" s="1" t="n"/>
+      <c r="L55" s="1" t="n"/>
+      <c r="M55" s="1" t="n"/>
+      <c r="N55" s="1" t="n"/>
+      <c r="O55" s="1" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>494261017</t>
+          <t>7847015</t>
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>G3114</t>
+          <t>G311-1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>G311400</t>
+          <t>G311.11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3135,12 +3125,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>494261017</t>
+          <t>7847015</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Worsening angina</t>
+          <t>Crescendo angina</t>
         </is>
       </c>
       <c r="H56" s="1" t="n">
@@ -3149,9 +3139,15 @@
       <c r="I56" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="1" t="n"/>
-      <c r="K56" s="1" t="n"/>
-      <c r="L56" s="1" t="n"/>
+      <c r="J56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="M56" s="1" t="n">
         <v>1</v>
       </c>
@@ -3165,35 +3161,35 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>264497018</t>
+          <t>634751000006116</t>
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>662Kz</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>662Kz00</t>
+          <t>322..00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>170593007</t>
+          <t>164861001</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>264492012</t>
+          <t>1205556017</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Angina control NOS</t>
+          <t>ECG myocardial ischaemia</t>
         </is>
       </c>
       <c r="H57" s="1" t="n">
@@ -3212,48 +3208,52 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>338974012</t>
+          <t>494261017</t>
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>G33z4</t>
+          <t>G3114</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>G33z400</t>
+          <t>G311400</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>225566008</t>
+          <t>4557003</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>338974012</t>
+          <t>494261017</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ischaemic chest pain</t>
+          <t>Worsening angina</t>
         </is>
       </c>
       <c r="H58" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I58" s="1" t="n"/>
+      <c r="I58" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="J58" s="1" t="n"/>
       <c r="K58" s="1" t="n"/>
       <c r="L58" s="1" t="n"/>
       <c r="M58" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="N58" s="1" t="n"/>
+      <c r="N58" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="O58" s="1" t="n">
         <v>1</v>
       </c>
@@ -3261,7 +3261,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>459859010</t>
+          <t>635641000006111</t>
         </is>
       </c>
       <c r="B59" s="1" t="n">
@@ -3269,27 +3269,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>G34z0</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>G34z000</t>
+          <t>3222.00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>315348000</t>
+          <t>164861001</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>459859010</t>
+          <t>1205556017</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Asymptomatic coronary heart disease</t>
+          <t>ECG:shows myocardial ischaemia</t>
         </is>
       </c>
       <c r="H59" s="1" t="n">
@@ -3308,7 +3308,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1142521000000115</t>
+          <t>264497018</t>
         </is>
       </c>
       <c r="B60" s="1" t="n">
@@ -3316,27 +3316,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>8CEJ</t>
+          <t>662Kz</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>8CEJ.00</t>
+          <t>662Kz00</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>513841000000103</t>
+          <t>170593007</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1142521000000115</t>
+          <t>264492012</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Coronary heart disease leaflet given</t>
+          <t>Angina control NOS</t>
         </is>
       </c>
       <c r="H60" s="1" t="n">
@@ -3355,82 +3355,84 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>451372015</t>
+          <t>338974012</t>
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>14AL</t>
+          <t>G33z4</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>14AL.00</t>
+          <t>G33z400</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>308068007</t>
+          <t>225566008</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>451372015</t>
+          <t>338974012</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>H/O: Treatment for ischaemic heart disease</t>
+          <t>Ischaemic chest pain</t>
         </is>
       </c>
       <c r="H61" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I61" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="I61" s="1" t="n"/>
       <c r="J61" s="1" t="n"/>
       <c r="K61" s="1" t="n"/>
       <c r="L61" s="1" t="n"/>
-      <c r="M61" s="1" t="n"/>
+      <c r="M61" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N61" s="1" t="n"/>
-      <c r="O61" s="1" t="n"/>
+      <c r="O61" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>7844010</t>
+          <t>459859010</t>
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>G311</t>
+          <t>G34z0</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>G311.00</t>
+          <t>G34z000</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>4557003</t>
+          <t>315348000</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>494262012</t>
+          <t>459859010</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Preinfarction syndrome</t>
+          <t>Asymptomatic coronary heart disease</t>
         </is>
       </c>
       <c r="H62" s="1" t="n">
@@ -3439,64 +3441,52 @@
       <c r="I62" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N62" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="J62" s="1" t="n"/>
+      <c r="K62" s="1" t="n"/>
+      <c r="L62" s="1" t="n"/>
+      <c r="M62" s="1" t="n"/>
+      <c r="N62" s="1" t="n"/>
+      <c r="O62" s="1" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>300436010</t>
+          <t>1142521000000115</t>
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>G70z</t>
+          <t>8CEJ</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>G70z.00</t>
+          <t>8CEJ.00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>72092001</t>
+          <t>513841000000103</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>119795011</t>
+          <t>1142521000000115</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Arteriosclerotic vascular disease NOS</t>
+          <t>Coronary heart disease leaflet given</t>
         </is>
       </c>
       <c r="H63" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I63" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" s="1" t="n"/>
       <c r="K63" s="1" t="n"/>
@@ -3508,7 +3498,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1235225010</t>
+          <t>451372015</t>
         </is>
       </c>
       <c r="B64" s="1" t="n">
@@ -3516,27 +3506,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>G331</t>
+          <t>14AL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>G331.00</t>
+          <t>14AL.00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>87343002</t>
+          <t>308068007</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1235225010</t>
+          <t>451372015</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Prinzmetal's angina</t>
+          <t>H/O: Treatment for ischaemic heart disease</t>
         </is>
       </c>
       <c r="H64" s="1" t="n">
@@ -3548,42 +3538,42 @@
       <c r="J64" s="1" t="n"/>
       <c r="K64" s="1" t="n"/>
       <c r="L64" s="1" t="n"/>
-      <c r="M64" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M64" s="1" t="n"/>
       <c r="N64" s="1" t="n"/>
-      <c r="O64" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O64" s="1" t="n"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1539331000006118</t>
+          <t>7844010</t>
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>EMISNOQFH3</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>G311</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>G311.00</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1539331000006102</t>
+          <t>4557003</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1539331000006118</t>
+          <t>494262012</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>H/O: coronary heart disease</t>
+          <t>Preinfarction syndrome</t>
         </is>
       </c>
       <c r="H65" s="1" t="n">
@@ -3592,52 +3582,64 @@
       <c r="I65" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="1" t="n"/>
-      <c r="K65" s="1" t="n"/>
-      <c r="L65" s="1" t="n"/>
-      <c r="M65" s="1" t="n"/>
-      <c r="N65" s="1" t="n"/>
-      <c r="O65" s="1" t="n"/>
+      <c r="J65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>451370011</t>
+          <t>300436010</t>
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>14AJ</t>
+          <t>G70z</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>14AJ.00</t>
+          <t>G70z.00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>308066006</t>
+          <t>72092001</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>451370011</t>
+          <t>119795011</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>H/O: Angina in last year</t>
+          <t>Arteriosclerotic vascular disease NOS</t>
         </is>
       </c>
       <c r="H66" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I66" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="1" t="n"/>
       <c r="K66" s="1" t="n"/>
@@ -3649,35 +3651,35 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>299834013</t>
+          <t>1235225010</t>
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>G3y</t>
+          <t>G331</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>G3y..00</t>
+          <t>G331.00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>414545008</t>
+          <t>87343002</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2534664018</t>
+          <t>1235225010</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Other specified ischaemic heart disease</t>
+          <t>Prinzmetal's angina</t>
         </is>
       </c>
       <c r="H67" s="1" t="n">
@@ -3700,7 +3702,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>498328016</t>
+          <t>1539331000006118</t>
         </is>
       </c>
       <c r="B68" s="1" t="n">
@@ -3708,27 +3710,23 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>G3112</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>G311200</t>
-        </is>
-      </c>
+          <t>EMISNOQFH3</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>59021001</t>
+          <t>1539331000006102</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>498328016</t>
+          <t>1539331000006118</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Angina at rest</t>
+          <t>H/O: coronary heart disease</t>
         </is>
       </c>
       <c r="H68" s="1" t="n">
@@ -3737,55 +3735,45 @@
       <c r="I68" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K68" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L68" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M68" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="J68" s="1" t="n"/>
+      <c r="K68" s="1" t="n"/>
+      <c r="L68" s="1" t="n"/>
+      <c r="M68" s="1" t="n"/>
       <c r="N68" s="1" t="n"/>
-      <c r="O68" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O68" s="1" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>350350014</t>
+          <t>451370011</t>
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>G33z6</t>
+          <t>14AJ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>G33z600</t>
+          <t>14AJ.00</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>233821000</t>
+          <t>308066006</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>350350014</t>
+          <t>451370011</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>New onset angina</t>
+          <t>H/O: Angina in last year</t>
         </is>
       </c>
       <c r="H69" s="1" t="n">
@@ -3797,46 +3785,42 @@
       <c r="J69" s="1" t="n"/>
       <c r="K69" s="1" t="n"/>
       <c r="L69" s="1" t="n"/>
-      <c r="M69" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M69" s="1" t="n"/>
       <c r="N69" s="1" t="n"/>
-      <c r="O69" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O69" s="1" t="n"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>451425016</t>
+          <t>299834013</t>
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>8B27</t>
+          <t>G3y</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>8B27.00</t>
+          <t>G3y..00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>308117007</t>
+          <t>414545008</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>451425016</t>
+          <t>2534664018</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Antianginal therapy</t>
+          <t>Other specified ischaemic heart disease</t>
         </is>
       </c>
       <c r="H70" s="1" t="n">
@@ -3848,42 +3832,46 @@
       <c r="J70" s="1" t="n"/>
       <c r="K70" s="1" t="n"/>
       <c r="L70" s="1" t="n"/>
-      <c r="M70" s="1" t="n"/>
+      <c r="M70" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N70" s="1" t="n"/>
-      <c r="O70" s="1" t="n"/>
+      <c r="O70" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1752201000000116</t>
+          <t>498328016</t>
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>G3112</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>187..00</t>
+          <t>G311200</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>704207005</t>
+          <t>59021001</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>3010438013</t>
+          <t>498328016</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Frequency of angina</t>
+          <t>Angina at rest</t>
         </is>
       </c>
       <c r="H71" s="1" t="n">
@@ -3892,17 +3880,27 @@
       <c r="I71" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="1" t="n"/>
-      <c r="K71" s="1" t="n"/>
-      <c r="L71" s="1" t="n"/>
-      <c r="M71" s="1" t="n"/>
+      <c r="J71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N71" s="1" t="n"/>
-      <c r="O71" s="1" t="n"/>
+      <c r="O71" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>491581000006110</t>
+          <t>350350014</t>
         </is>
       </c>
       <c r="B72" s="1" t="n">
@@ -3910,46 +3908,50 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>G70-1</t>
+          <t>G33z6</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>G70..11</t>
+          <t>G33z600</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>72092001</t>
+          <t>233821000</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>119795011</t>
+          <t>350350014</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Arteriosclerosis</t>
+          <t>New onset angina</t>
         </is>
       </c>
       <c r="H72" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I72" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" s="1" t="n"/>
       <c r="K72" s="1" t="n"/>
       <c r="L72" s="1" t="n"/>
-      <c r="M72" s="1" t="n"/>
+      <c r="M72" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N72" s="1" t="n"/>
-      <c r="O72" s="1" t="n"/>
+      <c r="O72" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>905381000006117</t>
+          <t>451425016</t>
         </is>
       </c>
       <c r="B73" s="1" t="n">
@@ -3957,23 +3959,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HNG0012</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>8B27</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>8B27.00</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>905381000006101</t>
+          <t>308117007</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>905381000006117</t>
+          <t>451425016</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[RFC] Angina</t>
+          <t>Antianginal therapy</t>
         </is>
       </c>
       <c r="H73" s="1" t="n">
@@ -3992,35 +3998,35 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>90731000000111</t>
+          <t>1752201000000116</t>
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9Ob1</t>
+          <t>187</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>9Ob1.00</t>
+          <t>187..00</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>315021005</t>
+          <t>704207005</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1785183019</t>
+          <t>3010438013</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Refuses coronary heart disease monitoring</t>
+          <t>Frequency of angina</t>
         </is>
       </c>
       <c r="H74" s="1" t="n">
@@ -4039,42 +4045,42 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>459483011</t>
+          <t>491581000006110</t>
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>8I37</t>
+          <t>G70-1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>8I37.00</t>
+          <t>G70..11</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>315021005</t>
+          <t>72092001</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>459483011</t>
+          <t>119795011</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Coronary heart disease monitoring refused</t>
+          <t>Arteriosclerosis</t>
         </is>
       </c>
       <c r="H75" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I75" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="1" t="n"/>
       <c r="K75" s="1" t="n"/>
@@ -4086,56 +4092,50 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2534674015</t>
+          <t>905381000006117</t>
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>G34y1</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>G34y100</t>
-        </is>
-      </c>
+          <t>HNG0012</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>413844008</t>
+          <t>905381000006101</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2534674015</t>
+          <t>905381000006117</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chronic myocardial ischaemia</t>
+          <t>[RFC] Angina</t>
         </is>
       </c>
       <c r="H76" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I76" s="1" t="n"/>
+      <c r="I76" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="J76" s="1" t="n"/>
       <c r="K76" s="1" t="n"/>
       <c r="L76" s="1" t="n"/>
-      <c r="M76" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M76" s="1" t="n"/>
       <c r="N76" s="1" t="n"/>
-      <c r="O76" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O76" s="1" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>39111000006114</t>
+          <t>90731000000111</t>
         </is>
       </c>
       <c r="B77" s="1" t="n">
@@ -4143,27 +4143,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>G31</t>
+          <t>9Ob1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>G31..00</t>
+          <t>9Ob1.00</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>414545008</t>
+          <t>315021005</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2534663012</t>
+          <t>1785183019</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Other acute and subacute ischaemic heart disease</t>
+          <t>Refuses coronary heart disease monitoring</t>
         </is>
       </c>
       <c r="H77" s="1" t="n">
@@ -4175,18 +4175,14 @@
       <c r="J77" s="1" t="n"/>
       <c r="K77" s="1" t="n"/>
       <c r="L77" s="1" t="n"/>
-      <c r="M77" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M77" s="1" t="n"/>
       <c r="N77" s="1" t="n"/>
-      <c r="O77" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O77" s="1" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>482911000006118</t>
+          <t>459483011</t>
         </is>
       </c>
       <c r="B78" s="1" t="n">
@@ -4194,23 +4190,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>EMISAN1</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>8I37</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>8I37.00</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>482911000006102</t>
+          <t>315021005</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>482911000006118</t>
+          <t>459483011</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Angina grading (canadian cardiovascular society)</t>
+          <t>Coronary heart disease monitoring refused</t>
         </is>
       </c>
       <c r="H78" s="1" t="n">
@@ -4229,7 +4229,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3371411000006113</t>
+          <t>2534674015</t>
         </is>
       </c>
       <c r="B79" s="1" t="n">
@@ -4237,23 +4237,27 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>^ESCTCH337141</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>G34y1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>G34y100</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>53741008</t>
+          <t>413844008</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2536397013</t>
+          <t>2534674015</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CHD - Coronary heart disease</t>
+          <t>Chronic myocardial ischaemia</t>
         </is>
       </c>
       <c r="H79" s="1" t="n">
@@ -4265,14 +4269,18 @@
       <c r="J79" s="1" t="n"/>
       <c r="K79" s="1" t="n"/>
       <c r="L79" s="1" t="n"/>
-      <c r="M79" s="1" t="n"/>
+      <c r="M79" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N79" s="1" t="n"/>
-      <c r="O79" s="1" t="n"/>
+      <c r="O79" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3371421000006117</t>
+          <t>39111000006114</t>
         </is>
       </c>
       <c r="B80" s="1" t="n">
@@ -4280,23 +4288,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>^ESCTCO337142</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>G31</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>G31..00</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>53741008</t>
+          <t>414545008</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2536398015</t>
+          <t>2534663012</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Coronary heart disease</t>
+          <t>Other acute and subacute ischaemic heart disease</t>
         </is>
       </c>
       <c r="H80" s="1" t="n">
@@ -4308,14 +4320,18 @@
       <c r="J80" s="1" t="n"/>
       <c r="K80" s="1" t="n"/>
       <c r="L80" s="1" t="n"/>
-      <c r="M80" s="1" t="n"/>
+      <c r="M80" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N80" s="1" t="n"/>
-      <c r="O80" s="1" t="n"/>
+      <c r="O80" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2117731000000119</t>
+          <t>482911000006118</t>
         </is>
       </c>
       <c r="B81" s="1" t="n">
@@ -4323,27 +4339,23 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>661M0</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>661M000</t>
-        </is>
-      </c>
+          <t>EMISAN1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>811901000000107</t>
+          <t>482911000006102</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2117731000000119</t>
+          <t>482911000006118</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Angina self-management plan agreed</t>
+          <t>Angina grading (canadian cardiovascular society)</t>
         </is>
       </c>
       <c r="H81" s="1" t="n">
@@ -4362,35 +4374,31 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>302275011</t>
+          <t>3371411000006113</t>
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>J0833</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>J083300</t>
-        </is>
-      </c>
+          <t>^ESCTCH337141</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>196542004</t>
+          <t>53741008</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>302275011</t>
+          <t>2536397013</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ludwig's angina</t>
+          <t>CHD - Coronary heart disease</t>
         </is>
       </c>
       <c r="H82" s="1" t="n">
@@ -4409,84 +4417,78 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>350354017</t>
+          <t>3371421000006117</t>
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>G344</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>G344.00</t>
-        </is>
-      </c>
+          <t>^ESCTCO337142</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>233823002</t>
+          <t>53741008</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>350354017</t>
+          <t>2536398015</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Silent myocardial ischaemia</t>
+          <t>Coronary heart disease</t>
         </is>
       </c>
       <c r="H83" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I83" s="1" t="n"/>
+      <c r="I83" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="J83" s="1" t="n"/>
       <c r="K83" s="1" t="n"/>
       <c r="L83" s="1" t="n"/>
-      <c r="M83" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M83" s="1" t="n"/>
       <c r="N83" s="1" t="n"/>
-      <c r="O83" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O83" s="1" t="n"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>299805019</t>
+          <t>2117731000000119</t>
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>G34z</t>
+          <t>661M0</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>G34z.00</t>
+          <t>661M000</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>413838009</t>
+          <t>811901000000107</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2534672016</t>
+          <t>2117731000000119</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Other chronic ischaemic heart disease NOS</t>
+          <t>Angina self-management plan agreed</t>
         </is>
       </c>
       <c r="H84" s="1" t="n">
@@ -4498,18 +4500,14 @@
       <c r="J84" s="1" t="n"/>
       <c r="K84" s="1" t="n"/>
       <c r="L84" s="1" t="n"/>
-      <c r="M84" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M84" s="1" t="n"/>
       <c r="N84" s="1" t="n"/>
-      <c r="O84" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O84" s="1" t="n"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>394541000006112</t>
+          <t>302275011</t>
         </is>
       </c>
       <c r="B85" s="1" t="n">
@@ -4517,27 +4515,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Gyu3</t>
+          <t>J0833</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Gyu3.00</t>
+          <t>J083300</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>414545008</t>
+          <t>196542004</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2534664018</t>
+          <t>302275011</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[X]Ischaemic heart diseases</t>
+          <t>Ludwig's angina</t>
         </is>
       </c>
       <c r="H85" s="1" t="n">
@@ -4549,18 +4547,14 @@
       <c r="J85" s="1" t="n"/>
       <c r="K85" s="1" t="n"/>
       <c r="L85" s="1" t="n"/>
-      <c r="M85" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M85" s="1" t="n"/>
       <c r="N85" s="1" t="n"/>
-      <c r="O85" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O85" s="1" t="n"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>89332015</t>
+          <t>350354017</t>
         </is>
       </c>
       <c r="B86" s="1" t="n">
@@ -4568,27 +4562,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>G3-2</t>
+          <t>G344</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>G3...12</t>
+          <t>G344.00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>443502000</t>
+          <t>233823002</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2842265012</t>
+          <t>350354017</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Atherosclerotic heart disease</t>
+          <t>Silent myocardial ischaemia</t>
         </is>
       </c>
       <c r="H86" s="1" t="n">
@@ -4600,14 +4594,18 @@
       <c r="J86" s="1" t="n"/>
       <c r="K86" s="1" t="n"/>
       <c r="L86" s="1" t="n"/>
-      <c r="M86" s="1" t="n"/>
+      <c r="M86" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N86" s="1" t="n"/>
-      <c r="O86" s="1" t="n"/>
+      <c r="O86" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>98087016</t>
+          <t>299805019</t>
         </is>
       </c>
       <c r="B87" s="1" t="n">
@@ -4615,27 +4613,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>G330</t>
+          <t>G34z</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>G330.00</t>
+          <t>G34z.00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>59021001</t>
+          <t>413838009</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>98087016</t>
+          <t>2534672016</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Angina decubitus</t>
+          <t>Other chronic ischaemic heart disease NOS</t>
         </is>
       </c>
       <c r="H87" s="1" t="n">
@@ -4658,7 +4656,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>856011000006116</t>
+          <t>394541000006112</t>
         </is>
       </c>
       <c r="B88" s="1" t="n">
@@ -4666,23 +4664,27 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>EMISAC3</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Gyu3</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Gyu3.00</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>856011000006100</t>
+          <t>414545008</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>856011000006116</t>
+          <t>2534664018</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Angina control - unsatisfactory</t>
+          <t>[X]Ischaemic heart diseases</t>
         </is>
       </c>
       <c r="H88" s="1" t="n">
@@ -4694,42 +4696,46 @@
       <c r="J88" s="1" t="n"/>
       <c r="K88" s="1" t="n"/>
       <c r="L88" s="1" t="n"/>
-      <c r="M88" s="1" t="n"/>
+      <c r="M88" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N88" s="1" t="n"/>
-      <c r="O88" s="1" t="n"/>
+      <c r="O88" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1216388013</t>
+          <t>89332015</t>
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ZV7B0-1</t>
+          <t>G3-2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ZV7B011</t>
+          <t>G3...12</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>171223006</t>
+          <t>443502000</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>265320019</t>
+          <t>2842265012</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[V]Screening for ischaemic heart disease (IHD)</t>
+          <t>Atherosclerotic heart disease</t>
         </is>
       </c>
       <c r="H89" s="1" t="n">
@@ -4748,31 +4754,35 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1856391000006112</t>
+          <t>98087016</t>
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>EMISNQCO168</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>G330</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>G330.00</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1856391000006108</t>
+          <t>59021001</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1856391000006112</t>
+          <t>98087016</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Coronary heart disease monitoring in primary care</t>
+          <t>Angina decubitus</t>
         </is>
       </c>
       <c r="H90" s="1" t="n">
@@ -4784,38 +4794,42 @@
       <c r="J90" s="1" t="n"/>
       <c r="K90" s="1" t="n"/>
       <c r="L90" s="1" t="n"/>
-      <c r="M90" s="1" t="n"/>
+      <c r="M90" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N90" s="1" t="n"/>
-      <c r="O90" s="1" t="n"/>
+      <c r="O90" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1895641000006114</t>
+          <t>856011000006116</t>
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>EMISNQON8</t>
+          <t>EMISAC3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1895641000006105</t>
+          <t>856011000006100</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1895641000006114</t>
+          <t>856011000006116</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>On coronary heart disease register</t>
+          <t>Angina control - unsatisfactory</t>
         </is>
       </c>
       <c r="H91" s="1" t="n">
@@ -4834,7 +4848,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4775971000006114</t>
+          <t>256451015</t>
         </is>
       </c>
       <c r="B92" s="1" t="n">
@@ -4842,23 +4856,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>^ESCTAN477597</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>322Z</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>322Z.00</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>194828000</t>
+          <t>164861001</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>299755016</t>
+          <t>1205556017</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Angina</t>
+          <t>ECG: myocardial ischaemia NOS</t>
         </is>
       </c>
       <c r="H92" s="1" t="n">
@@ -4870,18 +4888,14 @@
       <c r="J92" s="1" t="n"/>
       <c r="K92" s="1" t="n"/>
       <c r="L92" s="1" t="n"/>
-      <c r="M92" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M92" s="1" t="n"/>
       <c r="N92" s="1" t="n"/>
-      <c r="O92" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O92" s="1" t="n"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5887611000006117</t>
+          <t>1216388013</t>
         </is>
       </c>
       <c r="B93" s="1" t="n">
@@ -4889,23 +4903,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>^ESCTEX588761</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>ZV7B0-1</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ZV7B011</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>300995000</t>
+          <t>171223006</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>442203016</t>
+          <t>265320019</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Exercise-induced angina</t>
+          <t>[V]Screening for ischaemic heart disease (IHD)</t>
         </is>
       </c>
       <c r="H93" s="1" t="n">
@@ -4917,18 +4935,14 @@
       <c r="J93" s="1" t="n"/>
       <c r="K93" s="1" t="n"/>
       <c r="L93" s="1" t="n"/>
-      <c r="M93" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M93" s="1" t="n"/>
       <c r="N93" s="1" t="n"/>
-      <c r="O93" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O93" s="1" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>458410010</t>
+          <t>1856391000006112</t>
         </is>
       </c>
       <c r="B94" s="1" t="n">
@@ -4936,27 +4950,23 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>G33z5</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>G33z500</t>
-        </is>
-      </c>
+          <t>EMISNQCO168</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>314116003</t>
+          <t>1856391000006108</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>458410010</t>
+          <t>1856391000006112</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Post infarct angina</t>
+          <t>Coronary heart disease monitoring in primary care</t>
         </is>
       </c>
       <c r="H94" s="1" t="n">
@@ -4968,18 +4978,14 @@
       <c r="J94" s="1" t="n"/>
       <c r="K94" s="1" t="n"/>
       <c r="L94" s="1" t="n"/>
-      <c r="M94" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M94" s="1" t="n"/>
       <c r="N94" s="1" t="n"/>
-      <c r="O94" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O94" s="1" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>459487012</t>
+          <t>1895641000006114</t>
         </is>
       </c>
       <c r="B95" s="1" t="n">
@@ -4987,27 +4993,23 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>G3113</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>G311300</t>
-        </is>
-      </c>
+          <t>EMISNQON8</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>315025001</t>
+          <t>1895641000006105</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>459487012</t>
+          <t>1895641000006114</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Refractory angina</t>
+          <t>On coronary heart disease register</t>
         </is>
       </c>
       <c r="H95" s="1" t="n">
@@ -5019,20 +5021,14 @@
       <c r="J95" s="1" t="n"/>
       <c r="K95" s="1" t="n"/>
       <c r="L95" s="1" t="n"/>
-      <c r="M95" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N95" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O95" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M95" s="1" t="n"/>
+      <c r="N95" s="1" t="n"/>
+      <c r="O95" s="1" t="n"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>460687010</t>
+          <t>4775971000006114</t>
         </is>
       </c>
       <c r="B96" s="1" t="n">
@@ -5040,27 +5036,23 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ZV458</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>ZV45800</t>
-        </is>
-      </c>
+          <t>^ESCTAN477597</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>428375006</t>
+          <t>194828000</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2692299011</t>
+          <t>299755016</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>History of placement of stent for coronary artery disease</t>
+          <t>Angina</t>
         </is>
       </c>
       <c r="H96" s="1" t="n">
@@ -5072,14 +5064,18 @@
       <c r="J96" s="1" t="n"/>
       <c r="K96" s="1" t="n"/>
       <c r="L96" s="1" t="n"/>
-      <c r="M96" s="1" t="n"/>
+      <c r="M96" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N96" s="1" t="n"/>
-      <c r="O96" s="1" t="n"/>
+      <c r="O96" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2536393012</t>
+          <t>5887611000006117</t>
         </is>
       </c>
       <c r="B97" s="1" t="n">
@@ -5087,27 +5083,23 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>G3-1</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>G3...11</t>
-        </is>
-      </c>
+          <t>^ESCTEX588761</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>443502000</t>
+          <t>300995000</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2842265012</t>
+          <t>442203016</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Arteriosclerotic heart disease</t>
+          <t>Exercise-induced angina</t>
         </is>
       </c>
       <c r="H97" s="1" t="n">
@@ -5119,14 +5111,18 @@
       <c r="J97" s="1" t="n"/>
       <c r="K97" s="1" t="n"/>
       <c r="L97" s="1" t="n"/>
-      <c r="M97" s="1" t="n"/>
+      <c r="M97" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N97" s="1" t="n"/>
-      <c r="O97" s="1" t="n"/>
+      <c r="O97" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>482811000006113</t>
+          <t>458410010</t>
         </is>
       </c>
       <c r="B98" s="1" t="n">
@@ -5134,27 +5130,27 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>G311-4</t>
+          <t>G33z5</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>G311.14</t>
+          <t>G33z500</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>59021001</t>
+          <t>314116003</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>498328016</t>
+          <t>458410010</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Angina at rest</t>
+          <t>Post infarct angina</t>
         </is>
       </c>
       <c r="H98" s="1" t="n">
@@ -5163,15 +5159,9 @@
       <c r="I98" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J98" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K98" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L98" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="J98" s="1" t="n"/>
+      <c r="K98" s="1" t="n"/>
+      <c r="L98" s="1" t="n"/>
       <c r="M98" s="1" t="n">
         <v>1</v>
       </c>
@@ -5183,7 +5173,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>496991000006111</t>
+          <t>459487012</t>
         </is>
       </c>
       <c r="B99" s="1" t="n">
@@ -5191,27 +5181,27 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>G342</t>
+          <t>G3113</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>G342.00</t>
+          <t>G311300</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>72092001</t>
+          <t>315025001</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>119795011</t>
+          <t>459487012</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Atherosclerotic cardiovascular disease</t>
+          <t>Refractory angina</t>
         </is>
       </c>
       <c r="H99" s="1" t="n">
@@ -5223,14 +5213,20 @@
       <c r="J99" s="1" t="n"/>
       <c r="K99" s="1" t="n"/>
       <c r="L99" s="1" t="n"/>
-      <c r="M99" s="1" t="n"/>
-      <c r="N99" s="1" t="n"/>
-      <c r="O99" s="1" t="n"/>
+      <c r="M99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>960181000006111</t>
+          <t>459488019</t>
         </is>
       </c>
       <c r="B100" s="1" t="n">
@@ -5238,23 +5234,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>EMISCAN2</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>G31y3</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>G31y300</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>960181000006107</t>
+          <t>315026000</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>960181000006111</t>
+          <t>459488019</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Anginal pain</t>
+          <t>Transient myocardial ischaemia</t>
         </is>
       </c>
       <c r="H100" s="1" t="n">
@@ -5273,31 +5273,35 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6360391000006118</t>
+          <t>460687010</t>
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>^ESCTAT636039</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>ZV458</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ZV45800</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>371807002</t>
+          <t>428375006</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1210402019</t>
+          <t>2692299011</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Atypical angina</t>
+          <t>History of placement of stent for coronary artery disease</t>
         </is>
       </c>
       <c r="H101" s="1" t="n">
@@ -5309,48 +5313,42 @@
       <c r="J101" s="1" t="n"/>
       <c r="K101" s="1" t="n"/>
       <c r="L101" s="1" t="n"/>
-      <c r="M101" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N101" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O101" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M101" s="1" t="n"/>
+      <c r="N101" s="1" t="n"/>
+      <c r="O101" s="1" t="n"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>59952018</t>
+          <t>2536393012</t>
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>G3300</t>
+          <t>G3-1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>G330000</t>
+          <t>G3...11</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>35928006</t>
+          <t>443502000</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>59952018</t>
+          <t>2842265012</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nocturnal angina</t>
+          <t>Arteriosclerotic heart disease</t>
         </is>
       </c>
       <c r="H102" s="1" t="n">
@@ -5362,57 +5360,59 @@
       <c r="J102" s="1" t="n"/>
       <c r="K102" s="1" t="n"/>
       <c r="L102" s="1" t="n"/>
-      <c r="M102" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N102" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O102" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M102" s="1" t="n"/>
+      <c r="N102" s="1" t="n"/>
+      <c r="O102" s="1" t="n"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2537483013</t>
+          <t>482811000006113</t>
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>G34y0</t>
+          <t>G311-4</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>G34y000</t>
+          <t>G311.14</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>413844008</t>
+          <t>59021001</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2537483013</t>
+          <t>498328016</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chronic coronary insufficiency</t>
+          <t>Angina at rest</t>
         </is>
       </c>
       <c r="H103" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I103" s="1" t="n"/>
-      <c r="J103" s="1" t="n"/>
-      <c r="K103" s="1" t="n"/>
-      <c r="L103" s="1" t="n"/>
+      <c r="I103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="M103" s="1" t="n">
         <v>1</v>
       </c>
@@ -5424,31 +5424,35 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>6360351000006112</t>
+          <t>496991000006111</t>
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>^ESCTMU636035</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>G342</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>G342.00</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>371803003</t>
+          <t>72092001</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1210398011</t>
+          <t>119795011</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Multi vessel coronary artery disease</t>
+          <t>Atherosclerotic cardiovascular disease</t>
         </is>
       </c>
       <c r="H104" s="1" t="n">
@@ -5467,35 +5471,31 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1780448012</t>
+          <t>960181000006111</t>
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>9Ob7</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>9Ob7.00</t>
-        </is>
-      </c>
+          <t>EMISCAN2</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>401254000</t>
+          <t>960181000006107</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1780448012</t>
+          <t>960181000006111</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Coronary heart disease monitoring deleted</t>
+          <t>Anginal pain</t>
         </is>
       </c>
       <c r="H105" s="1" t="n">
@@ -5514,31 +5514,31 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7518331000006115</t>
+          <t>6360391000006118</t>
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>^ESCTCO751833</t>
+          <t>^ESCTAT636039</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>699196002</t>
+          <t>371807002</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2982986018</t>
+          <t>1210402019</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Coronary artery disease excluded</t>
+          <t>Atypical angina</t>
         </is>
       </c>
       <c r="H106" s="1" t="n">
@@ -5550,38 +5550,48 @@
       <c r="J106" s="1" t="n"/>
       <c r="K106" s="1" t="n"/>
       <c r="L106" s="1" t="n"/>
-      <c r="M106" s="1" t="n"/>
-      <c r="N106" s="1" t="n"/>
-      <c r="O106" s="1" t="n"/>
+      <c r="M106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O106" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>12734391000006116</t>
+          <t>59952018</t>
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>^ESCT1273439</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>G3300</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>G330000</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>143451000000101</t>
+          <t>35928006</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1628371000000114</t>
+          <t>59952018</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>QOF (Quality and Outcomes Framework) secondary prevention of coronary heart disease quality indicator-related care invitation using preferred method of communication</t>
+          <t>Nocturnal angina</t>
         </is>
       </c>
       <c r="H107" s="1" t="n">
@@ -5593,42 +5603,48 @@
       <c r="J107" s="1" t="n"/>
       <c r="K107" s="1" t="n"/>
       <c r="L107" s="1" t="n"/>
-      <c r="M107" s="1" t="n"/>
-      <c r="N107" s="1" t="n"/>
-      <c r="O107" s="1" t="n"/>
+      <c r="M107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>299723016</t>
+          <t>2537483013</t>
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>G31y</t>
+          <t>G34y0</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>G31y.00</t>
+          <t>G34y000</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>414545008</t>
+          <t>413844008</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2534663012</t>
+          <t>2537483013</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Other acute and subacute ischaemic heart disease</t>
+          <t>Chronic coronary insufficiency</t>
         </is>
       </c>
       <c r="H108" s="1" t="n">
@@ -5651,42 +5667,38 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>300200014</t>
+          <t>6360351000006112</t>
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>G5y2</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>G5y2.00</t>
-        </is>
-      </c>
+          <t>^ESCTMU636035</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>72092001</t>
+          <t>371803003</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>119795011</t>
+          <t>1210398011</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cardiovascular arteriosclerosis unspecified</t>
+          <t>Multi vessel coronary artery disease</t>
         </is>
       </c>
       <c r="H109" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I109" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109" s="1" t="n"/>
       <c r="K109" s="1" t="n"/>
@@ -5698,35 +5710,35 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>144819018</t>
+          <t>1780448012</t>
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>G331-1</t>
+          <t>9Ob7</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>G331.11</t>
+          <t>9Ob7.00</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>87343002</t>
+          <t>401254000</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1235225010</t>
+          <t>1780448012</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Variant angina pectoris</t>
+          <t>Coronary heart disease monitoring deleted</t>
         </is>
       </c>
       <c r="H110" s="1" t="n">
@@ -5738,42 +5750,38 @@
       <c r="J110" s="1" t="n"/>
       <c r="K110" s="1" t="n"/>
       <c r="L110" s="1" t="n"/>
-      <c r="M110" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M110" s="1" t="n"/>
       <c r="N110" s="1" t="n"/>
-      <c r="O110" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O110" s="1" t="n"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1823891000006113</t>
+          <t>7518331000006115</t>
         </is>
       </c>
       <c r="B111" s="1" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>EMISNQCO148</t>
+          <t>^ESCTCO751833</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1823891000006109</t>
+          <t>699196002</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1823891000006113</t>
+          <t>2982986018</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Coronary heart disease confirmed</t>
+          <t>Coronary artery disease excluded</t>
         </is>
       </c>
       <c r="H111" s="1" t="n">
@@ -5792,76 +5800,78 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>6864781000006110</t>
+          <t>12734391000006116</t>
         </is>
       </c>
       <c r="B112" s="1" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>^ESCTMY686478</t>
+          <t>^ESCT1273439</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>414795007</t>
+          <t>143451000000101</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2534666016</t>
+          <t>1628371000000114</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Myocardial ischaemia</t>
+          <t>QOF (Quality and Outcomes Framework) secondary prevention of coronary heart disease quality indicator-related care invitation using preferred method of communication</t>
         </is>
       </c>
       <c r="H112" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I112" s="1" t="n"/>
+      <c r="I112" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="J112" s="1" t="n"/>
       <c r="K112" s="1" t="n"/>
       <c r="L112" s="1" t="n"/>
-      <c r="M112" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M112" s="1" t="n"/>
       <c r="N112" s="1" t="n"/>
-      <c r="O112" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O112" s="1" t="n"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>7105241000006116</t>
+          <t>299723016</t>
         </is>
       </c>
       <c r="B113" s="1" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>^ESCTTY710524</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>G31y</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>G31y.00</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>429559004</t>
+          <t>414545008</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2692821011</t>
+          <t>2534663012</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Typical angina</t>
+          <t>Other acute and subacute ischaemic heart disease</t>
         </is>
       </c>
       <c r="H113" s="1" t="n">
@@ -5884,80 +5894,82 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>494438016</t>
+          <t>300200014</t>
         </is>
       </c>
       <c r="B114" s="1" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>G31y2</t>
+          <t>G5y2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>G31y200</t>
+          <t>G5y2.00</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>46109009</t>
+          <t>72092001</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>494438016</t>
+          <t>119795011</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Subendocardial ischaemia</t>
+          <t>Cardiovascular arteriosclerosis unspecified</t>
         </is>
       </c>
       <c r="H114" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I114" s="1" t="n"/>
+      <c r="I114" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="J114" s="1" t="n"/>
       <c r="K114" s="1" t="n"/>
       <c r="L114" s="1" t="n"/>
-      <c r="M114" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M114" s="1" t="n"/>
       <c r="N114" s="1" t="n"/>
-      <c r="O114" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O114" s="1" t="n"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>8459561000006118</t>
+          <t>144819018</t>
         </is>
       </c>
       <c r="B115" s="1" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>^ESCTCO845956</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>G331-1</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>G331.11</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1083131000000100</t>
+          <t>87343002</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2714191000000119</t>
+          <t>1235225010</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Coronary heart disease monitoring invitation email</t>
+          <t>Variant angina pectoris</t>
         </is>
       </c>
       <c r="H115" s="1" t="n">
@@ -5969,42 +5981,42 @@
       <c r="J115" s="1" t="n"/>
       <c r="K115" s="1" t="n"/>
       <c r="L115" s="1" t="n"/>
-      <c r="M115" s="1" t="n"/>
+      <c r="M115" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N115" s="1" t="n"/>
-      <c r="O115" s="1" t="n"/>
+      <c r="O115" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>300874013</t>
+          <t>1823891000006113</t>
         </is>
       </c>
       <c r="B116" s="1" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Gyu30</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Gyu3000</t>
-        </is>
-      </c>
+          <t>EMISNQCO148</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>194828000</t>
+          <t>1823891000006109</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>299757012</t>
+          <t>1823891000006113</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>[X]Other forms of angina pectoris</t>
+          <t>Coronary heart disease confirmed</t>
         </is>
       </c>
       <c r="H116" s="1" t="n">
@@ -6016,46 +6028,38 @@
       <c r="J116" s="1" t="n"/>
       <c r="K116" s="1" t="n"/>
       <c r="L116" s="1" t="n"/>
-      <c r="M116" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M116" s="1" t="n"/>
       <c r="N116" s="1" t="n"/>
-      <c r="O116" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O116" s="1" t="n"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>482801000006110</t>
+          <t>6864781000006110</t>
         </is>
       </c>
       <c r="B117" s="1" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>J421-1</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>J421.11</t>
-        </is>
-      </c>
+          <t>^ESCTMY686478</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>241154007</t>
+          <t>414795007</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>361157010</t>
+          <t>2534666016</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Abdominal angina</t>
+          <t>Myocardial ischaemia</t>
         </is>
       </c>
       <c r="H117" s="1" t="n">
@@ -6067,42 +6071,42 @@
       <c r="J117" s="1" t="n"/>
       <c r="K117" s="1" t="n"/>
       <c r="L117" s="1" t="n"/>
-      <c r="M117" s="1" t="n"/>
+      <c r="M117" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N117" s="1" t="n"/>
-      <c r="O117" s="1" t="n"/>
+      <c r="O117" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>299804015</t>
+          <t>7105241000006116</t>
         </is>
       </c>
       <c r="B118" s="1" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>G34yz</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>G34yz00</t>
-        </is>
-      </c>
+          <t>^ESCTTY710524</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>413838009</t>
+          <t>429559004</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2534671011</t>
+          <t>2692821011</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Other specified chronic ischaemic heart disease NOS</t>
+          <t>Typical angina</t>
         </is>
       </c>
       <c r="H118" s="1" t="n">
@@ -6125,43 +6129,41 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>299800012</t>
+          <t>494438016</t>
         </is>
       </c>
       <c r="B119" s="1" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>G34y</t>
+          <t>G31y2</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>G34y.00</t>
+          <t>G31y200</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>413838009</t>
+          <t>46109009</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2534671011</t>
+          <t>494438016</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Other specified chronic ischaemic heart disease</t>
+          <t>Subendocardial ischaemia</t>
         </is>
       </c>
       <c r="H119" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I119" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="I119" s="1" t="n"/>
       <c r="J119" s="1" t="n"/>
       <c r="K119" s="1" t="n"/>
       <c r="L119" s="1" t="n"/>
@@ -6176,7 +6178,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>300959012</t>
+          <t>8459561000006118</t>
         </is>
       </c>
       <c r="B120" s="1" t="n">
@@ -6184,34 +6186,30 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Gyu70</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Gyu7000</t>
-        </is>
-      </c>
+          <t>^ESCTCO845956</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>72092001</t>
+          <t>1083131000000100</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>119795011</t>
+          <t>2714191000000119</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>[X]Atherosclerosis of other arteries</t>
+          <t>Coronary heart disease monitoring invitation email</t>
         </is>
       </c>
       <c r="H120" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I120" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" s="1" t="n"/>
       <c r="K120" s="1" t="n"/>
@@ -6223,31 +6221,35 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>14639991000006115</t>
+          <t>300874013</t>
         </is>
       </c>
       <c r="B121" s="1" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>^ESCT1463999</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
+          <t>Gyu30</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Gyu3000</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>275931000</t>
+          <t>194828000</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>4634330015</t>
+          <t>299757012</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Administration of prophylactic aspirin for ischaemic heart disease</t>
+          <t>[X]Other forms of angina pectoris</t>
         </is>
       </c>
       <c r="H121" s="1" t="n">
@@ -6259,38 +6261,46 @@
       <c r="J121" s="1" t="n"/>
       <c r="K121" s="1" t="n"/>
       <c r="L121" s="1" t="n"/>
-      <c r="M121" s="1" t="n"/>
+      <c r="M121" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N121" s="1" t="n"/>
-      <c r="O121" s="1" t="n"/>
+      <c r="O121" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>5887631000006111</t>
+          <t>482801000006110</t>
         </is>
       </c>
       <c r="B122" s="1" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>^ESCTEX588763</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t>J421-1</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>J421.11</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>300995000</t>
+          <t>241154007</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>442205011</t>
+          <t>361157010</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Exertional angina</t>
+          <t>Abdominal angina</t>
         </is>
       </c>
       <c r="H122" s="1" t="n">
@@ -6302,57 +6312,57 @@
       <c r="J122" s="1" t="n"/>
       <c r="K122" s="1" t="n"/>
       <c r="L122" s="1" t="n"/>
-      <c r="M122" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M122" s="1" t="n"/>
       <c r="N122" s="1" t="n"/>
-      <c r="O122" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O122" s="1" t="n"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>6546111000006118</t>
+          <t>299804015</t>
         </is>
       </c>
       <c r="B123" s="1" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>^ESCTAC654611</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
+          <t>G34yz</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>G34yz00</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>394659003</t>
+          <t>413838009</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2579561010</t>
+          <t>2534671011</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>ACS - Acute coronary syndrome</t>
+          <t>Other specified chronic ischaemic heart disease NOS</t>
         </is>
       </c>
       <c r="H123" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I123" s="1" t="n"/>
+      <c r="I123" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="J123" s="1" t="n"/>
       <c r="K123" s="1" t="n"/>
       <c r="L123" s="1" t="n"/>
       <c r="M123" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="N123" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="N123" s="1" t="n"/>
       <c r="O123" s="1" t="n">
         <v>1</v>
       </c>
@@ -6360,35 +6370,35 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>299750014</t>
+          <t>299800012</t>
         </is>
       </c>
       <c r="B124" s="1" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>G31yz</t>
+          <t>G34y</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>G31yz00</t>
+          <t>G34y.00</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>414545008</t>
+          <t>413838009</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2534663012</t>
+          <t>2534671011</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Other acute and subacute ischaemic heart disease NOS</t>
+          <t>Other specified chronic ischaemic heart disease</t>
         </is>
       </c>
       <c r="H124" s="1" t="n">
@@ -6411,54 +6421,54 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>6860251000006115</t>
+          <t>300959012</t>
         </is>
       </c>
       <c r="B125" s="1" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>^ESCTIS686025</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
+          <t>Gyu70</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Gyu7000</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>414545008</t>
+          <t>72092001</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2534663012</t>
+          <t>119795011</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ischemic heart disease</t>
+          <t>[X]Atherosclerosis of other arteries</t>
         </is>
       </c>
       <c r="H125" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I125" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J125" s="1" t="n"/>
       <c r="K125" s="1" t="n"/>
       <c r="L125" s="1" t="n"/>
-      <c r="M125" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M125" s="1" t="n"/>
       <c r="N125" s="1" t="n"/>
-      <c r="O125" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O125" s="1" t="n"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3371381000006110</t>
+          <t>931961000006117</t>
         </is>
       </c>
       <c r="B126" s="1" t="n">
@@ -6466,42 +6476,50 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>^ESCTCA337138</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
+          <t>G31y0-99</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>G31y099</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>53741008</t>
+          <t>194823009</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2536394018</t>
+          <t>931961000006117</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>CAD - Coronary artery disease</t>
+          <t>Acute coronary syndrome</t>
         </is>
       </c>
       <c r="H126" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I126" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" s="1" t="n"/>
       <c r="K126" s="1" t="n"/>
       <c r="L126" s="1" t="n"/>
-      <c r="M126" s="1" t="n"/>
+      <c r="M126" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N126" s="1" t="n"/>
-      <c r="O126" s="1" t="n"/>
+      <c r="O126" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>299763015</t>
+          <t>14639991000006115</t>
         </is>
       </c>
       <c r="B127" s="1" t="n">
@@ -6509,27 +6527,23 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>G330z</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>G330z00</t>
-        </is>
-      </c>
+          <t>^ESCT1463999</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>59021001</t>
+          <t>275931000</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>98087016</t>
+          <t>4634330015</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Angina decubitus NOS</t>
+          <t>Administration of prophylactic aspirin for ischaemic heart disease</t>
         </is>
       </c>
       <c r="H127" s="1" t="n">
@@ -6541,18 +6555,14 @@
       <c r="J127" s="1" t="n"/>
       <c r="K127" s="1" t="n"/>
       <c r="L127" s="1" t="n"/>
-      <c r="M127" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M127" s="1" t="n"/>
       <c r="N127" s="1" t="n"/>
-      <c r="O127" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O127" s="1" t="n"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2117311000000111</t>
+          <t>5887631000006111</t>
         </is>
       </c>
       <c r="B128" s="1" t="n">
@@ -6560,27 +6570,23 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>661N0</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>661N000</t>
-        </is>
-      </c>
+          <t>^ESCTEX588763</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>811701000000105</t>
+          <t>300995000</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2117311000000111</t>
+          <t>442205011</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Angina self-management plan review</t>
+          <t>Exertional angina</t>
         </is>
       </c>
       <c r="H128" s="1" t="n">
@@ -6592,14 +6598,18 @@
       <c r="J128" s="1" t="n"/>
       <c r="K128" s="1" t="n"/>
       <c r="L128" s="1" t="n"/>
-      <c r="M128" s="1" t="n"/>
+      <c r="M128" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N128" s="1" t="n"/>
-      <c r="O128" s="1" t="n"/>
+      <c r="O128" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>854491000006113</t>
+          <t>6546111000006118</t>
         </is>
       </c>
       <c r="B129" s="1" t="n">
@@ -6607,48 +6617,46 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>EGTON458</t>
+          <t>^ESCTAC654611</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>854491000006109</t>
+          <t>394659003</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>854491000006113</t>
+          <t>2579561010</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Unstable angina</t>
+          <t>ACS - Acute coronary syndrome</t>
         </is>
       </c>
       <c r="H129" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I129" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K129" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L129" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M129" s="1" t="n"/>
-      <c r="N129" s="1" t="n"/>
-      <c r="O129" s="1" t="n"/>
+      <c r="I129" s="1" t="n"/>
+      <c r="J129" s="1" t="n"/>
+      <c r="K129" s="1" t="n"/>
+      <c r="L129" s="1" t="n"/>
+      <c r="M129" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N129" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>3920021000006112</t>
+          <t>6860251000006115</t>
         </is>
       </c>
       <c r="B130" s="1" t="n">
@@ -6656,23 +6664,23 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>^ESCTCO392002</t>
+          <t>^ESCTIS686025</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>87343002</t>
+          <t>414545008</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1235224014</t>
+          <t>2534663012</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Coronary artery spasm angina</t>
+          <t>Ischemic heart disease</t>
         </is>
       </c>
       <c r="H130" s="1" t="n">
@@ -6695,7 +6703,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1900651000006110</t>
+          <t>299750014</t>
         </is>
       </c>
       <c r="B131" s="1" t="n">
@@ -6703,27 +6711,27 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2Ba22</t>
+          <t>G31yz</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2Ba2200</t>
+          <t>G31yz00</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>914991000000106</t>
+          <t>414545008</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2350961000000113</t>
+          <t>2534663012</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Surveillance of Cerebral Palsy in Europe classification - predominant pattern C.3 - infarct of the middle cerebral artery</t>
+          <t>Other acute and subacute ischaemic heart disease NOS</t>
         </is>
       </c>
       <c r="H131" s="1" t="n">
@@ -6735,87 +6743,89 @@
       <c r="J131" s="1" t="n"/>
       <c r="K131" s="1" t="n"/>
       <c r="L131" s="1" t="n"/>
-      <c r="M131" s="1" t="n"/>
+      <c r="M131" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N131" s="1" t="n"/>
-      <c r="O131" s="1" t="n"/>
+      <c r="O131" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>36036010</t>
+          <t>3371381000006110</t>
         </is>
       </c>
       <c r="B132" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>G33z2</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>G33z200</t>
-        </is>
-      </c>
+          <t>^ESCTCA337138</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>21470009</t>
+          <t>53741008</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>36036010</t>
+          <t>2536394018</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Syncope anginosa</t>
+          <t>CAD - Coronary artery disease</t>
         </is>
       </c>
       <c r="H132" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I132" s="1" t="n"/>
+      <c r="I132" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="J132" s="1" t="n"/>
       <c r="K132" s="1" t="n"/>
       <c r="L132" s="1" t="n"/>
-      <c r="M132" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M132" s="1" t="n"/>
       <c r="N132" s="1" t="n"/>
-      <c r="O132" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O132" s="1" t="n"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>5056201000006111</t>
+          <t>299763015</t>
         </is>
       </c>
       <c r="B133" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>^ESCTTR505620</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>G330z</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>G330z00</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>233817007</t>
+          <t>59021001</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2535923015</t>
+          <t>98087016</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Triple vessel coronary artery disease</t>
+          <t>Angina decubitus NOS</t>
         </is>
       </c>
       <c r="H133" s="1" t="n">
@@ -6827,38 +6837,46 @@
       <c r="J133" s="1" t="n"/>
       <c r="K133" s="1" t="n"/>
       <c r="L133" s="1" t="n"/>
-      <c r="M133" s="1" t="n"/>
+      <c r="M133" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N133" s="1" t="n"/>
-      <c r="O133" s="1" t="n"/>
+      <c r="O133" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>6360361000006114</t>
+          <t>2117311000000111</t>
         </is>
       </c>
       <c r="B134" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>^ESCTLE636036</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>661N0</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>661N000</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>371804009</t>
+          <t>811701000000105</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>1210399015</t>
+          <t>2117311000000111</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Left main coronary artery disease</t>
+          <t>Angina self-management plan review</t>
         </is>
       </c>
       <c r="H134" s="1" t="n">
@@ -6877,35 +6895,31 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1551191000000111</t>
+          <t>854491000006113</t>
         </is>
       </c>
       <c r="B135" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>1I11</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>1I11.00</t>
-        </is>
-      </c>
+          <t>EGTON458</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>473146006</t>
+          <t>854491000006109</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2955884019</t>
+          <t>854491000006113</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Coronary artery disease excluded</t>
+          <t>Unstable angina</t>
         </is>
       </c>
       <c r="H135" s="1" t="n">
@@ -6914,9 +6928,15 @@
       <c r="I135" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J135" s="1" t="n"/>
-      <c r="K135" s="1" t="n"/>
-      <c r="L135" s="1" t="n"/>
+      <c r="J135" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L135" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="M135" s="1" t="n"/>
       <c r="N135" s="1" t="n"/>
       <c r="O135" s="1" t="n"/>
@@ -6924,35 +6944,31 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>585631000000113</t>
+          <t>3920021000006112</t>
         </is>
       </c>
       <c r="B136" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>8H2V</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>8H2V.00</t>
-        </is>
-      </c>
+          <t>^ESCTCO392002</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>699245006</t>
+          <t>87343002</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>3082941013</t>
+          <t>1235224014</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Emergency hospital admission for ischaemic heart disease</t>
+          <t>Coronary artery spasm angina</t>
         </is>
       </c>
       <c r="H136" s="1" t="n">
@@ -6964,38 +6980,46 @@
       <c r="J136" s="1" t="n"/>
       <c r="K136" s="1" t="n"/>
       <c r="L136" s="1" t="n"/>
-      <c r="M136" s="1" t="n"/>
+      <c r="M136" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N136" s="1" t="n"/>
-      <c r="O136" s="1" t="n"/>
+      <c r="O136" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>7573181000006118</t>
+          <t>1900651000006110</t>
         </is>
       </c>
       <c r="B137" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>^ESCTHE757318</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
+          <t>2Ba22</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2Ba2200</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>703273002</t>
+          <t>914991000000106</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>3008136010</t>
+          <t>2350961000000113</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Heart failure with reduced ejection fraction due to coronary artery disease</t>
+          <t>Surveillance of Cerebral Palsy in Europe classification - predominant pattern C.3 - infarct of the middle cerebral artery</t>
         </is>
       </c>
       <c r="H137" s="1" t="n">
@@ -7014,7 +7038,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1731551000000112</t>
+          <t>36036010</t>
         </is>
       </c>
       <c r="B138" s="1" t="n">
@@ -7022,77 +7046,79 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>662K4</t>
+          <t>G33z2</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>662K400</t>
+          <t>G33z200</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>775161000000102</t>
+          <t>21470009</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>1731551000000112</t>
+          <t>36036010</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Angina self management plan commenced</t>
+          <t>Syncope anginosa</t>
         </is>
       </c>
       <c r="H138" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I138" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="I138" s="1" t="n"/>
       <c r="J138" s="1" t="n"/>
       <c r="K138" s="1" t="n"/>
       <c r="L138" s="1" t="n"/>
-      <c r="M138" s="1" t="n"/>
+      <c r="M138" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N138" s="1" t="n"/>
-      <c r="O138" s="1" t="n"/>
+      <c r="O138" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>4776071000006117</t>
+          <t>5056201000006111</t>
         </is>
       </c>
       <c r="B139" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>^ESCTTW477607</t>
+          <t>^ESCTTR505620</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>194843003</t>
+          <t>233817007</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>299784013</t>
+          <t>2535923015</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Two coronary vessel disease</t>
+          <t>Triple vessel coronary artery disease</t>
         </is>
       </c>
       <c r="H139" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I139" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J139" s="1" t="n"/>
       <c r="K139" s="1" t="n"/>
@@ -7104,31 +7130,35 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>6860261000006118</t>
+          <t>412682010</t>
         </is>
       </c>
       <c r="B140" s="1" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>^ESCTIH686026</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
+          <t>Q494</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Q494.00</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>414545008</t>
+          <t>276517000</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2537479013</t>
+          <t>412682010</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>IHD - Ischemic heart disease</t>
+          <t>Transient myocardial ischaemia of newborn</t>
         </is>
       </c>
       <c r="H140" s="1" t="n">
@@ -7140,42 +7170,38 @@
       <c r="J140" s="1" t="n"/>
       <c r="K140" s="1" t="n"/>
       <c r="L140" s="1" t="n"/>
-      <c r="M140" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M140" s="1" t="n"/>
       <c r="N140" s="1" t="n"/>
-      <c r="O140" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O140" s="1" t="n"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3166141000006114</t>
+          <t>6360361000006114</t>
         </is>
       </c>
       <c r="B141" s="1" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>^ESCTAN316614</t>
+          <t>^ESCTLE636036</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>41334000</t>
+          <t>371804009</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>68946011</t>
+          <t>1210399015</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Angina, class II</t>
+          <t>Left main coronary artery disease</t>
         </is>
       </c>
       <c r="H141" s="1" t="n">
@@ -7187,42 +7213,42 @@
       <c r="J141" s="1" t="n"/>
       <c r="K141" s="1" t="n"/>
       <c r="L141" s="1" t="n"/>
-      <c r="M141" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M141" s="1" t="n"/>
       <c r="N141" s="1" t="n"/>
-      <c r="O141" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O141" s="1" t="n"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>7475751000006117</t>
+          <t>1551191000000111</t>
         </is>
       </c>
       <c r="B142" s="1" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>^ESCTIS747575</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
+          <t>1I11</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>1I11.00</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>472100003</t>
+          <t>473146006</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2951007019</t>
+          <t>2955884019</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ischaemic dilated cardiomyopathy due to coronary artery disease</t>
+          <t>Coronary artery disease excluded</t>
         </is>
       </c>
       <c r="H142" s="1" t="n">
@@ -7241,35 +7267,35 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>300879015</t>
+          <t>585631000000113</t>
         </is>
       </c>
       <c r="B143" s="1" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Gyu33</t>
+          <t>8H2V</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Gyu3300</t>
+          <t>8H2V.00</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>413838009</t>
+          <t>699245006</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2534671011</t>
+          <t>3082941013</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>[X]Other forms of chronic ischaemic heart disease</t>
+          <t>Emergency hospital admission for ischaemic heart disease</t>
         </is>
       </c>
       <c r="H143" s="1" t="n">
@@ -7281,46 +7307,38 @@
       <c r="J143" s="1" t="n"/>
       <c r="K143" s="1" t="n"/>
       <c r="L143" s="1" t="n"/>
-      <c r="M143" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M143" s="1" t="n"/>
       <c r="N143" s="1" t="n"/>
-      <c r="O143" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O143" s="1" t="n"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1731571000000115</t>
+          <t>7573181000006118</t>
         </is>
       </c>
       <c r="B144" s="1" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>662K5</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>662K500</t>
-        </is>
-      </c>
+          <t>^ESCTHE757318</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>775171000000109</t>
+          <t>703273002</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>1731571000000115</t>
+          <t>3008136010</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Angina self management plan completed</t>
+          <t>Heart failure with reduced ejection fraction due to coronary artery disease</t>
         </is>
       </c>
       <c r="H144" s="1" t="n">
@@ -7339,35 +7357,35 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>300876010</t>
+          <t>1731551000000112</t>
         </is>
       </c>
       <c r="B145" s="1" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Gyu32</t>
+          <t>662K4</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Gyu3200</t>
+          <t>662K400</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>414545008</t>
+          <t>775161000000102</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2534663012</t>
+          <t>1731551000000112</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>[X]Other forms of acute ischaemic heart disease</t>
+          <t>Angina self management plan commenced</t>
         </is>
       </c>
       <c r="H145" s="1" t="n">
@@ -7379,42 +7397,38 @@
       <c r="J145" s="1" t="n"/>
       <c r="K145" s="1" t="n"/>
       <c r="L145" s="1" t="n"/>
-      <c r="M145" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M145" s="1" t="n"/>
       <c r="N145" s="1" t="n"/>
-      <c r="O145" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O145" s="1" t="n"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>3371361000006117</t>
+          <t>4776071000006117</t>
         </is>
       </c>
       <c r="B146" s="1" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>^ESCTCO337136</t>
+          <t>^ESCTTW477607</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>53741008</t>
+          <t>194843003</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>89331010</t>
+          <t>299784013</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Coronary arteriosclerosis</t>
+          <t>Two coronary vessel disease</t>
         </is>
       </c>
       <c r="H146" s="1" t="n">
@@ -7433,35 +7447,31 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2210191000000118</t>
+          <t>6860261000006118</t>
         </is>
       </c>
       <c r="B147" s="1" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>8T04</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>8T04.00</t>
-        </is>
-      </c>
+          <t>^ESCTIH686026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>853561000000109</t>
+          <t>414545008</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2210191000000118</t>
+          <t>2537479013</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Referral to Angina Plan self-management programme</t>
+          <t>IHD - Ischemic heart disease</t>
         </is>
       </c>
       <c r="H147" s="1" t="n">
@@ -7473,38 +7483,42 @@
       <c r="J147" s="1" t="n"/>
       <c r="K147" s="1" t="n"/>
       <c r="L147" s="1" t="n"/>
-      <c r="M147" s="1" t="n"/>
+      <c r="M147" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N147" s="1" t="n"/>
-      <c r="O147" s="1" t="n"/>
+      <c r="O147" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>3919991000006112</t>
+          <t>3166141000006114</t>
         </is>
       </c>
       <c r="B148" s="1" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>^ESCTPR391999</t>
+          <t>^ESCTAN316614</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>87343002</t>
+          <t>41334000</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>144818014</t>
+          <t>68946011</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Prinzmetal angina</t>
+          <t>Angina, class II</t>
         </is>
       </c>
       <c r="H148" s="1" t="n">
@@ -7527,31 +7541,31 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1856401000006114</t>
+          <t>7475751000006117</t>
         </is>
       </c>
       <c r="B149" s="1" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>EMISNQCO169</t>
+          <t>^ESCTIS747575</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>1856401000006105</t>
+          <t>472100003</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>1856401000006114</t>
+          <t>2951007019</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Coronary heart disease monitoring in secondary care</t>
+          <t>Ischaemic dilated cardiomyopathy due to coronary artery disease</t>
         </is>
       </c>
       <c r="H149" s="1" t="n">
@@ -7570,35 +7584,35 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>32122016</t>
+          <t>300879015</t>
         </is>
       </c>
       <c r="B150" s="1" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>G33z0</t>
+          <t>Gyu33</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>G33z000</t>
+          <t>Gyu3300</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>19057007</t>
+          <t>413838009</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>32122016</t>
+          <t>2534671011</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Status anginosus</t>
+          <t>[X]Other forms of chronic ischaemic heart disease</t>
         </is>
       </c>
       <c r="H150" s="1" t="n">
@@ -7613,9 +7627,7 @@
       <c r="M150" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="N150" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="N150" s="1" t="n"/>
       <c r="O150" s="1" t="n">
         <v>1</v>
       </c>
@@ -7623,31 +7635,35 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>6841231000006113</t>
+          <t>1731571000000115</t>
         </is>
       </c>
       <c r="B151" s="1" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>^ESCTAC684123</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
+          <t>662K5</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>662K500</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>413439005</t>
+          <t>775171000000109</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2534668015</t>
+          <t>1731571000000115</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Acute ischaemic heart disease</t>
+          <t>Angina self management plan completed</t>
         </is>
       </c>
       <c r="H151" s="1" t="n">
@@ -7659,53 +7675,49 @@
       <c r="J151" s="1" t="n"/>
       <c r="K151" s="1" t="n"/>
       <c r="L151" s="1" t="n"/>
-      <c r="M151" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M151" s="1" t="n"/>
       <c r="N151" s="1" t="n"/>
-      <c r="O151" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O151" s="1" t="n"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>299758019</t>
+          <t>300876010</t>
         </is>
       </c>
       <c r="B152" s="1" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>G33z1</t>
+          <t>Gyu32</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>G33z100</t>
+          <t>Gyu3200</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>194828000</t>
+          <t>414545008</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>299758019</t>
+          <t>2534663012</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Stenocardia</t>
+          <t>[X]Other forms of acute ischaemic heart disease</t>
         </is>
       </c>
       <c r="H152" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I152" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J152" s="1" t="n"/>
       <c r="K152" s="1" t="n"/>
@@ -7721,129 +7733,129 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>4776031000006115</t>
+          <t>3371361000006117</t>
         </is>
       </c>
       <c r="B153" s="1" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>^ESCTIS477603</t>
+          <t>^ESCTCO337136</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>194828000</t>
+          <t>53741008</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>299762013</t>
+          <t>89331010</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ischaemic heart disease - angina</t>
+          <t>Coronary arteriosclerosis</t>
         </is>
       </c>
       <c r="H153" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I153" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" s="1" t="n"/>
       <c r="K153" s="1" t="n"/>
       <c r="L153" s="1" t="n"/>
-      <c r="M153" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M153" s="1" t="n"/>
       <c r="N153" s="1" t="n"/>
-      <c r="O153" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O153" s="1" t="n"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>6841391000006118</t>
+          <t>2210191000000118</t>
         </is>
       </c>
       <c r="B154" s="1" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>^ESCTAC684139</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
+          <t>8T04</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>8T04.00</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>413444003</t>
+          <t>853561000000109</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2534670012</t>
+          <t>2210191000000118</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Acute myocardial ischaemia</t>
+          <t>Referral to Angina Plan self-management programme</t>
         </is>
       </c>
       <c r="H154" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I154" s="1" t="n"/>
+      <c r="I154" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="J154" s="1" t="n"/>
       <c r="K154" s="1" t="n"/>
       <c r="L154" s="1" t="n"/>
-      <c r="M154" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M154" s="1" t="n"/>
       <c r="N154" s="1" t="n"/>
-      <c r="O154" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O154" s="1" t="n"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>7502661000006117</t>
+          <t>3919991000006112</t>
         </is>
       </c>
       <c r="B155" s="1" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>^ESCTMI750266</t>
+          <t>^ESCTPR391999</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>697976003</t>
+          <t>87343002</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2968395019</t>
+          <t>144818014</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Microvascular ischaemia of myocardium</t>
+          <t>Prinzmetal angina</t>
         </is>
       </c>
       <c r="H155" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I155" s="1" t="n"/>
+      <c r="I155" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="J155" s="1" t="n"/>
       <c r="K155" s="1" t="n"/>
       <c r="L155" s="1" t="n"/>
@@ -7858,31 +7870,31 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>7518321000006118</t>
+          <t>1856401000006114</t>
         </is>
       </c>
       <c r="B156" s="1" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>^ESCTCO751832</t>
+          <t>EMISNQCO169</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>699196002</t>
+          <t>1856401000006105</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2983022014</t>
+          <t>1856401000006114</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Coronary artery disease absent</t>
+          <t>Coronary heart disease monitoring in secondary care</t>
         </is>
       </c>
       <c r="H156" s="1" t="n">
@@ -7901,31 +7913,35 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3920011000006116</t>
+          <t>32122016</t>
         </is>
       </c>
       <c r="B157" s="1" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>^ESCTVA392001</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
+          <t>G33z0</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>G33z000</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>87343002</t>
+          <t>19057007</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>1235223015</t>
+          <t>32122016</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Variant angina</t>
+          <t>Status anginosus</t>
         </is>
       </c>
       <c r="H157" s="1" t="n">
@@ -7940,7 +7956,9 @@
       <c r="M157" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="N157" s="1" t="n"/>
+      <c r="N157" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="O157" s="1" t="n">
         <v>1</v>
       </c>
@@ -7948,31 +7966,31 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>9868461000006110</t>
+          <t>6841231000006113</t>
         </is>
       </c>
       <c r="B158" s="1" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>^ESCTUN986846</t>
+          <t>^ESCTAC684123</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>15960061000119102</t>
+          <t>413439005</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>3323416014</t>
+          <t>2534668015</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Unstable angina co-occurrent and due to coronary arteriosclerosis</t>
+          <t>Acute ischaemic heart disease</t>
         </is>
       </c>
       <c r="H158" s="1" t="n">
@@ -7987,9 +8005,7 @@
       <c r="M158" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="N158" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="N158" s="1" t="n"/>
       <c r="O158" s="1" t="n">
         <v>1</v>
       </c>
@@ -7997,38 +8013,42 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>3499001000006116</t>
+          <t>299758019</t>
         </is>
       </c>
       <c r="B159" s="1" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>^ESCTAN349900</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>G33z1</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>G33z100</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>61490001</t>
+          <t>194828000</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>102153019</t>
+          <t>299758019</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Angina, class I</t>
+          <t>Stenocardia</t>
         </is>
       </c>
       <c r="H159" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I159" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J159" s="1" t="n"/>
       <c r="K159" s="1" t="n"/>
@@ -8044,37 +8064,39 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>7572351000006115</t>
+          <t>4776031000006115</t>
         </is>
       </c>
       <c r="B160" s="1" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>^ESCTSI757235</t>
+          <t>^ESCTIS477603</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>703214003</t>
+          <t>194828000</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>3007338016</t>
+          <t>299762013</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Silent coronary vasospastic disease</t>
+          <t>Ischaemic heart disease - angina</t>
         </is>
       </c>
       <c r="H160" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I160" s="1" t="n"/>
+      <c r="I160" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="J160" s="1" t="n"/>
       <c r="K160" s="1" t="n"/>
       <c r="L160" s="1" t="n"/>
@@ -8089,31 +8111,31 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4776051000006110</t>
+          <t>6841391000006118</t>
         </is>
       </c>
       <c r="B161" s="1" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>^ESCTSI477605</t>
+          <t>^ESCTAC684139</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>194842008</t>
+          <t>413444003</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2535853014</t>
+          <t>2534670012</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Single vessel coronary artery disease</t>
+          <t>Acute myocardial ischaemia</t>
         </is>
       </c>
       <c r="H161" s="1" t="n">
@@ -8125,81 +8147,87 @@
       <c r="J161" s="1" t="n"/>
       <c r="K161" s="1" t="n"/>
       <c r="L161" s="1" t="n"/>
-      <c r="M161" s="1" t="n"/>
+      <c r="M161" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N161" s="1" t="n"/>
-      <c r="O161" s="1" t="n"/>
+      <c r="O161" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>7483491000006110</t>
+          <t>7502661000006117</t>
         </is>
       </c>
       <c r="B162" s="1" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>^ESCTCO748349</t>
+          <t>^ESCTMI750266</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>473146006</t>
+          <t>697976003</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2955964017</t>
+          <t>2968395019</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Coronary arteriosclerosis excluded</t>
+          <t>Microvascular ischaemia of myocardium</t>
         </is>
       </c>
       <c r="H162" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I162" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="I162" s="1" t="n"/>
       <c r="J162" s="1" t="n"/>
       <c r="K162" s="1" t="n"/>
       <c r="L162" s="1" t="n"/>
-      <c r="M162" s="1" t="n"/>
+      <c r="M162" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N162" s="1" t="n"/>
-      <c r="O162" s="1" t="n"/>
+      <c r="O162" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3516223013</t>
+          <t>7518321000006118</t>
         </is>
       </c>
       <c r="B163" s="1" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>^ESCT1166277</t>
+          <t>^ESCTCO751832</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>736059007</t>
+          <t>699196002</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>3516223013</t>
+          <t>2983022014</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Angina self management plan</t>
+          <t>Coronary artery disease absent</t>
         </is>
       </c>
       <c r="H163" s="1" t="n">
@@ -8218,31 +8246,31 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>3886751000006118</t>
+          <t>3920011000006116</t>
         </is>
       </c>
       <c r="B164" s="1" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>^ESCTAN388675</t>
+          <t>^ESCTVA392001</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>85284003</t>
+          <t>87343002</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>141382014</t>
+          <t>1235223015</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Angina, class III</t>
+          <t>Variant angina</t>
         </is>
       </c>
       <c r="H164" s="1" t="n">
@@ -8265,31 +8293,31 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1047381000006114</t>
+          <t>9868461000006110</t>
         </is>
       </c>
       <c r="B165" s="1" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ALLERGY20868NEMIS</t>
+          <t>^ESCTUN986846</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>1047381000006105</t>
+          <t>15960061000119102</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>1047381000006114</t>
+          <t>3323416014</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Adverse reaction to Trangina Xl</t>
+          <t>Unstable angina co-occurrent and due to coronary arteriosclerosis</t>
         </is>
       </c>
       <c r="H165" s="1" t="n">
@@ -8301,38 +8329,44 @@
       <c r="J165" s="1" t="n"/>
       <c r="K165" s="1" t="n"/>
       <c r="L165" s="1" t="n"/>
-      <c r="M165" s="1" t="n"/>
-      <c r="N165" s="1" t="n"/>
-      <c r="O165" s="1" t="n"/>
+      <c r="M165" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N165" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O165" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>4776081000006119</t>
+          <t>3499001000006116</t>
         </is>
       </c>
       <c r="B166" s="1" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>^ESCTDO477608</t>
+          <t>^ESCTAN349900</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>194843003</t>
+          <t>61490001</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2535854015</t>
+          <t>102153019</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Double vessel coronary artery disease</t>
+          <t>Angina, class I</t>
         </is>
       </c>
       <c r="H166" s="1" t="n">
@@ -8344,81 +8378,87 @@
       <c r="J166" s="1" t="n"/>
       <c r="K166" s="1" t="n"/>
       <c r="L166" s="1" t="n"/>
-      <c r="M166" s="1" t="n"/>
+      <c r="M166" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N166" s="1" t="n"/>
-      <c r="O166" s="1" t="n"/>
+      <c r="O166" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>14658371000006113</t>
+          <t>7572351000006115</t>
         </is>
       </c>
       <c r="B167" s="1" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>^ESCT1465837</t>
+          <t>^ESCTSI757235</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>315021005</t>
+          <t>703214003</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>4590635013</t>
+          <t>3007338016</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Coronary heart disease monitoring declined</t>
+          <t>Silent coronary vasospastic disease</t>
         </is>
       </c>
       <c r="H167" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I167" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="I167" s="1" t="n"/>
       <c r="J167" s="1" t="n"/>
       <c r="K167" s="1" t="n"/>
       <c r="L167" s="1" t="n"/>
-      <c r="M167" s="1" t="n"/>
+      <c r="M167" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N167" s="1" t="n"/>
-      <c r="O167" s="1" t="n"/>
+      <c r="O167" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>6360421000006114</t>
+          <t>4776051000006110</t>
         </is>
       </c>
       <c r="B168" s="1" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>^ESCTRE636042</t>
+          <t>^ESCTSI477605</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>371809004</t>
+          <t>194842008</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2470266016</t>
+          <t>2535853014</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Recurrent angina after coronary stent placement</t>
+          <t>Single vessel coronary artery disease</t>
         </is>
       </c>
       <c r="H168" s="1" t="n">
@@ -8430,101 +8470,81 @@
       <c r="J168" s="1" t="n"/>
       <c r="K168" s="1" t="n"/>
       <c r="L168" s="1" t="n"/>
-      <c r="M168" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M168" s="1" t="n"/>
       <c r="N168" s="1" t="n"/>
-      <c r="O168" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O168" s="1" t="n"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2571561000006118</t>
+          <t>7483491000006110</t>
         </is>
       </c>
       <c r="B169" s="1" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>^ESCTPR257156</t>
+          <t>^ESCTCO748349</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>4557003</t>
+          <t>473146006</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>494262012</t>
+          <t>2955964017</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pre-infarction syndrome</t>
+          <t>Coronary arteriosclerosis excluded</t>
         </is>
       </c>
       <c r="H169" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I169" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J169" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K169" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L169" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M169" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N169" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O169" s="1" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J169" s="1" t="n"/>
+      <c r="K169" s="1" t="n"/>
+      <c r="L169" s="1" t="n"/>
+      <c r="M169" s="1" t="n"/>
+      <c r="N169" s="1" t="n"/>
+      <c r="O169" s="1" t="n"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2210251000000115</t>
+          <t>3516223013</t>
         </is>
       </c>
       <c r="B170" s="1" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>8IEY</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>8IEY.00</t>
-        </is>
-      </c>
+          <t>^ESCT1166277</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>853591000000103</t>
+          <t>736059007</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2210251000000115</t>
+          <t>3516223013</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Referral to Angina Plan self-management programme declined</t>
+          <t>Angina self management plan</t>
         </is>
       </c>
       <c r="H170" s="1" t="n">
@@ -8543,31 +8563,31 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>6650571000006114</t>
+          <t>3886751000006118</t>
         </is>
       </c>
       <c r="B171" s="1" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>^ESCTCO665057</t>
+          <t>^ESCTAN388675</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>401247006</t>
+          <t>85284003</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1780441018</t>
+          <t>141382014</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Coronary heart disease monitoring status</t>
+          <t>Angina, class III</t>
         </is>
       </c>
       <c r="H171" s="1" t="n">
@@ -8579,38 +8599,42 @@
       <c r="J171" s="1" t="n"/>
       <c r="K171" s="1" t="n"/>
       <c r="L171" s="1" t="n"/>
-      <c r="M171" s="1" t="n"/>
+      <c r="M171" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N171" s="1" t="n"/>
-      <c r="O171" s="1" t="n"/>
+      <c r="O171" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>12276271000006112</t>
+          <t>1047381000006114</t>
         </is>
       </c>
       <c r="B172" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>^ESCT1227627</t>
+          <t>ALLERGY20868NEMIS</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>371806006</t>
+          <t>1047381000006105</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>3673888019</t>
+          <t>1047381000006114</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Progressive angina</t>
+          <t>Adverse reaction to Trangina Xl</t>
         </is>
       </c>
       <c r="H172" s="1" t="n">
@@ -8622,42 +8646,38 @@
       <c r="J172" s="1" t="n"/>
       <c r="K172" s="1" t="n"/>
       <c r="L172" s="1" t="n"/>
-      <c r="M172" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M172" s="1" t="n"/>
       <c r="N172" s="1" t="n"/>
-      <c r="O172" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O172" s="1" t="n"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>6360401000006116</t>
+          <t>4776081000006119</t>
         </is>
       </c>
       <c r="B173" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>^ESCTRE636040</t>
+          <t>^ESCTDO477608</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>371808007</t>
+          <t>194843003</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2470265017</t>
+          <t>2535854015</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Recurrent angina after percutaneous transluminal coronary angioplasty</t>
+          <t>Double vessel coronary artery disease</t>
         </is>
       </c>
       <c r="H173" s="1" t="n">
@@ -8669,42 +8689,38 @@
       <c r="J173" s="1" t="n"/>
       <c r="K173" s="1" t="n"/>
       <c r="L173" s="1" t="n"/>
-      <c r="M173" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M173" s="1" t="n"/>
       <c r="N173" s="1" t="n"/>
-      <c r="O173" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O173" s="1" t="n"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>7966931000006114</t>
+          <t>14658371000006113</t>
         </is>
       </c>
       <c r="B174" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>^ESCTAN796693</t>
+          <t>^ESCT1465837</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>791000119109</t>
+          <t>315021005</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2967773018</t>
+          <t>4590635013</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Angina associated with type 2 diabetes mellitus</t>
+          <t>Coronary heart disease monitoring declined</t>
         </is>
       </c>
       <c r="H174" s="1" t="n">
@@ -8716,42 +8732,38 @@
       <c r="J174" s="1" t="n"/>
       <c r="K174" s="1" t="n"/>
       <c r="L174" s="1" t="n"/>
-      <c r="M174" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M174" s="1" t="n"/>
       <c r="N174" s="1" t="n"/>
-      <c r="O174" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O174" s="1" t="n"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>11927021000006117</t>
+          <t>6360421000006114</t>
         </is>
       </c>
       <c r="B175" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>^ESCT1192702</t>
+          <t>^ESCTRE636042</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>134438001</t>
+          <t>371809004</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>216244010</t>
+          <t>2470266016</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Canadian Cardiovascular Society classification of angina</t>
+          <t>Recurrent angina after coronary stent placement</t>
         </is>
       </c>
       <c r="H175" s="1" t="n">
@@ -8763,38 +8775,42 @@
       <c r="J175" s="1" t="n"/>
       <c r="K175" s="1" t="n"/>
       <c r="L175" s="1" t="n"/>
-      <c r="M175" s="1" t="n"/>
+      <c r="M175" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N175" s="1" t="n"/>
-      <c r="O175" s="1" t="n"/>
+      <c r="O175" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>4776001000006111</t>
+          <t>2571561000006118</t>
         </is>
       </c>
       <c r="B176" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>^ESCTAN477600</t>
+          <t>^ESCTPR257156</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>194828000</t>
+          <t>4557003</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>299759010</t>
+          <t>494262012</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Anginal syndrome</t>
+          <t>Pre-infarction syndrome</t>
         </is>
       </c>
       <c r="H176" s="1" t="n">
@@ -8803,13 +8819,21 @@
       <c r="I176" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="J176" s="1" t="n"/>
-      <c r="K176" s="1" t="n"/>
-      <c r="L176" s="1" t="n"/>
+      <c r="J176" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K176" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L176" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="M176" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="N176" s="1" t="n"/>
+      <c r="N176" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="O176" s="1" t="n">
         <v>1</v>
       </c>
@@ -8817,35 +8841,35 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>494260016</t>
+          <t>2210251000000115</t>
         </is>
       </c>
       <c r="B177" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>G311-2</t>
+          <t>8IEY</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>G311.12</t>
+          <t>8IEY.00</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>25106000</t>
+          <t>853591000000103</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>42087013</t>
+          <t>2210251000000115</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Impending infarction</t>
+          <t>Referral to Angina Plan self-management programme declined</t>
         </is>
       </c>
       <c r="H177" s="1" t="n">
@@ -8857,44 +8881,38 @@
       <c r="J177" s="1" t="n"/>
       <c r="K177" s="1" t="n"/>
       <c r="L177" s="1" t="n"/>
-      <c r="M177" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N177" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O177" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M177" s="1" t="n"/>
+      <c r="N177" s="1" t="n"/>
+      <c r="O177" s="1" t="n"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>8240941000006118</t>
+          <t>6650571000006114</t>
         </is>
       </c>
       <c r="B178" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>^ESCTAN824094</t>
+          <t>^ESCTCO665057</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>772471000000106</t>
+          <t>401247006</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>1724231000000118</t>
+          <t>1780441018</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Angina self management plan declined</t>
+          <t>Coronary heart disease monitoring status</t>
         </is>
       </c>
       <c r="H178" s="1" t="n">
@@ -8913,31 +8931,31 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>5887641000006118</t>
+          <t>12276271000006112</t>
         </is>
       </c>
       <c r="B179" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>^ESCTAN588764</t>
+          <t>^ESCT1227627</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>300995000</t>
+          <t>371806006</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>442206012</t>
+          <t>3673888019</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Angina of effort</t>
+          <t>Progressive angina</t>
         </is>
       </c>
       <c r="H179" s="1" t="n">
@@ -8960,74 +8978,78 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>6053011000006114</t>
+          <t>6360401000006116</t>
         </is>
       </c>
       <c r="B180" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>^ESCTRE605301</t>
+          <t>^ESCTRE636040</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>315021005</t>
+          <t>371808007</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>1785182012</t>
+          <t>2470265017</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Refuses CHD monitoring</t>
+          <t>Recurrent angina after percutaneous transluminal coronary angioplasty</t>
         </is>
       </c>
       <c r="H180" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I180" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J180" s="1" t="n"/>
       <c r="K180" s="1" t="n"/>
       <c r="L180" s="1" t="n"/>
-      <c r="M180" s="1" t="n"/>
+      <c r="M180" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N180" s="1" t="n"/>
-      <c r="O180" s="1" t="n"/>
+      <c r="O180" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>6360441000006119</t>
+          <t>7966931000006114</t>
         </is>
       </c>
       <c r="B181" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>^ESCTRE636044</t>
+          <t>^ESCTAN796693</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>371810009</t>
+          <t>791000119109</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2470267013</t>
+          <t>2967773018</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Recurrent angina after coronary artery bypass graft</t>
+          <t>Angina associated with type 2 diabetes mellitus</t>
         </is>
       </c>
       <c r="H181" s="1" t="n">
@@ -9050,31 +9072,31 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>6847761000006118</t>
+          <t>11927021000006117</t>
         </is>
       </c>
       <c r="B182" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>^ESCTCH684776</t>
+          <t>^ESCT1192702</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>413838009</t>
+          <t>134438001</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2534671011</t>
+          <t>216244010</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chronic ischemic heart disease</t>
+          <t>Canadian Cardiovascular Society classification of angina</t>
         </is>
       </c>
       <c r="H182" s="1" t="n">
@@ -9086,91 +9108,97 @@
       <c r="J182" s="1" t="n"/>
       <c r="K182" s="1" t="n"/>
       <c r="L182" s="1" t="n"/>
-      <c r="M182" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M182" s="1" t="n"/>
       <c r="N182" s="1" t="n"/>
-      <c r="O182" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O182" s="1" t="n"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>7278491000006111</t>
+          <t>4776001000006111</t>
         </is>
       </c>
       <c r="B183" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>^ESCTAT727849</t>
+          <t>^ESCTAN477600</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>443502000</t>
+          <t>194828000</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2842574013</t>
+          <t>299759010</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Atherosclerosis of coronary artery</t>
+          <t>Anginal syndrome</t>
         </is>
       </c>
       <c r="H183" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I183" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J183" s="1" t="n"/>
       <c r="K183" s="1" t="n"/>
       <c r="L183" s="1" t="n"/>
-      <c r="M183" s="1" t="n"/>
+      <c r="M183" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N183" s="1" t="n"/>
-      <c r="O183" s="1" t="n"/>
+      <c r="O183" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>7696501000006114</t>
+          <t>494260016</t>
         </is>
       </c>
       <c r="B184" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>^ESCTRE769650</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>G311-2</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>G311.12</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>712866001</t>
+          <t>25106000</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>3286157013</t>
+          <t>42087013</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Resting ischaemia</t>
+          <t>Impending infarction</t>
         </is>
       </c>
       <c r="H184" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I184" s="1" t="n"/>
+      <c r="I184" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="J184" s="1" t="n"/>
       <c r="K184" s="1" t="n"/>
       <c r="L184" s="1" t="n"/>
@@ -9187,31 +9215,31 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>7703511000006110</t>
+          <t>8240941000006118</t>
         </is>
       </c>
       <c r="B185" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>^ESCTSU770351</t>
+          <t>^ESCTAN824094</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>713405002</t>
+          <t>772471000000106</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>3289285016</t>
+          <t>1724231000000118</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Subacute ischaemic heart disease</t>
+          <t>Angina self management plan declined</t>
         </is>
       </c>
       <c r="H185" s="1" t="n">
@@ -9223,18 +9251,14 @@
       <c r="J185" s="1" t="n"/>
       <c r="K185" s="1" t="n"/>
       <c r="L185" s="1" t="n"/>
-      <c r="M185" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M185" s="1" t="n"/>
       <c r="N185" s="1" t="n"/>
-      <c r="O185" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O185" s="1" t="n"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>8259701000006112</t>
+          <t>5887641000006118</t>
         </is>
       </c>
       <c r="B186" s="1" t="n">
@@ -9242,23 +9266,23 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>^ESCTRE825970</t>
+          <t>^ESCTAN588764</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>809581000000109</t>
+          <t>300995000</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2112861000000118</t>
+          <t>442206012</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Referral to coronary heart disease clinic</t>
+          <t>Angina of effort</t>
         </is>
       </c>
       <c r="H186" s="1" t="n">
@@ -9270,45 +9294,49 @@
       <c r="J186" s="1" t="n"/>
       <c r="K186" s="1" t="n"/>
       <c r="L186" s="1" t="n"/>
-      <c r="M186" s="1" t="n"/>
+      <c r="M186" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N186" s="1" t="n"/>
-      <c r="O186" s="1" t="n"/>
+      <c r="O186" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>4540501000006118</t>
+          <t>6053011000006114</t>
         </is>
       </c>
       <c r="B187" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>^ESCTHI454050</t>
+          <t>^ESCTRE605301</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>161504004</t>
+          <t>315021005</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2986318019</t>
+          <t>1785182012</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>History of angina pectoris</t>
+          <t>Refuses CHD monitoring</t>
         </is>
       </c>
       <c r="H187" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I187" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J187" s="1" t="n"/>
       <c r="K187" s="1" t="n"/>
@@ -9320,31 +9348,31 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>6946631000006113</t>
+          <t>6360441000006119</t>
         </is>
       </c>
       <c r="B188" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>^ESCTOB694663</t>
+          <t>^ESCTRE636044</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>420006002</t>
+          <t>371810009</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2578015012</t>
+          <t>2470267013</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Obliterative coronary artery disease</t>
+          <t>Recurrent angina after coronary artery bypass graft</t>
         </is>
       </c>
       <c r="H188" s="1" t="n">
@@ -9356,38 +9384,42 @@
       <c r="J188" s="1" t="n"/>
       <c r="K188" s="1" t="n"/>
       <c r="L188" s="1" t="n"/>
-      <c r="M188" s="1" t="n"/>
+      <c r="M188" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N188" s="1" t="n"/>
-      <c r="O188" s="1" t="n"/>
+      <c r="O188" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>14194701000006115</t>
+          <t>6847761000006118</t>
         </is>
       </c>
       <c r="B189" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>^ESCT1419470</t>
+          <t>^ESCTCH684776</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>726499301000119105</t>
+          <t>413838009</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>4030229011</t>
+          <t>2534671011</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Myocardial infarction due to atherothrombotic coronary artery disease</t>
+          <t>Chronic ischemic heart disease</t>
         </is>
       </c>
       <c r="H189" s="1" t="n">
@@ -9399,45 +9431,49 @@
       <c r="J189" s="1" t="n"/>
       <c r="K189" s="1" t="n"/>
       <c r="L189" s="1" t="n"/>
-      <c r="M189" s="1" t="n"/>
+      <c r="M189" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N189" s="1" t="n"/>
-      <c r="O189" s="1" t="n"/>
+      <c r="O189" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1576311000006117</t>
+          <t>7278491000006111</t>
         </is>
       </c>
       <c r="B190" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>EGTON2G44</t>
+          <t>^ESCTAT727849</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>1576311000006101</t>
+          <t>443502000</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>1576311000006117</t>
+          <t>2842574013</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Cause of Death- Angina Pectoris</t>
+          <t>Atherosclerosis of coronary artery</t>
         </is>
       </c>
       <c r="H190" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I190" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J190" s="1" t="n"/>
       <c r="K190" s="1" t="n"/>
@@ -9449,74 +9485,78 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5056471000006118</t>
+          <t>7696501000006114</t>
         </is>
       </c>
       <c r="B191" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>^ESCTAC505647</t>
+          <t>^ESCTRE769650</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>233844002</t>
+          <t>712866001</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>350378010</t>
+          <t>3286157013</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Accelerated coronary artery disease in transplanted heart</t>
+          <t>Resting ischaemia</t>
         </is>
       </c>
       <c r="H191" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I191" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="I191" s="1" t="n"/>
       <c r="J191" s="1" t="n"/>
       <c r="K191" s="1" t="n"/>
       <c r="L191" s="1" t="n"/>
-      <c r="M191" s="1" t="n"/>
-      <c r="N191" s="1" t="n"/>
-      <c r="O191" s="1" t="n"/>
+      <c r="M191" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N191" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O191" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>3458791000006114</t>
+          <t>7703511000006110</t>
         </is>
       </c>
       <c r="B192" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>^ESCTAN345879</t>
+          <t>^ESCTSU770351</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>59021001</t>
+          <t>713405002</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>98088014</t>
+          <t>3289285016</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Anginal chest pain at rest</t>
+          <t>Subacute ischaemic heart disease</t>
         </is>
       </c>
       <c r="H192" s="1" t="n">
@@ -9539,35 +9579,31 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1900601000006111</t>
+          <t>8259701000006112</t>
         </is>
       </c>
       <c r="B193" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2Ba11</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>2Ba1100</t>
-        </is>
-      </c>
+          <t>^ESCTRE825970</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>914891000000100</t>
+          <t>809581000000109</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2350711000000114</t>
+          <t>2112861000000118</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Surveillance of Cerebral Palsy in Europe classification - predominant pattern B.2 - sequelae of intraventricular haemorrhage or periventricular infarction</t>
+          <t>Referral to coronary heart disease clinic</t>
         </is>
       </c>
       <c r="H193" s="1" t="n">
@@ -9586,31 +9622,31 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>8032161000006112</t>
+          <t>4540501000006118</t>
         </is>
       </c>
       <c r="B194" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>^ESCTCO803216</t>
+          <t>^ESCTHI454050</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>103011000119106</t>
+          <t>161504004</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>3290272012</t>
+          <t>2986318019</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Coronary arteriosclerosis in patient with history of previous myocardial infarction</t>
+          <t>History of angina pectoris</t>
         </is>
       </c>
       <c r="H194" s="1" t="n">
@@ -9629,31 +9665,31 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>14179491000006111</t>
+          <t>6946631000006113</t>
         </is>
       </c>
       <c r="B195" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>^ESCT1417949</t>
+          <t>^ESCTOB694663</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>15960341000119104</t>
+          <t>420006002</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>3991458017</t>
+          <t>2578015012</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Unstable angina due to arteriosclerosis of coronary artery bypass graft of transplanted heart</t>
+          <t>Obliterative coronary artery disease</t>
         </is>
       </c>
       <c r="H195" s="1" t="n">
@@ -9672,31 +9708,31 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>12125971000006114</t>
+          <t>1576311000006117</t>
         </is>
       </c>
       <c r="B196" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>^ESCT1212597</t>
+          <t>EGTON2G44</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>15960661000119107</t>
+          <t>1576311000006101</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>3645129018</t>
+          <t>1576311000006117</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Unstable angina co-occurrent and due to arteriosclerosis of coronary artery bypass graft</t>
+          <t>Cause of Death- Angina Pectoris</t>
         </is>
       </c>
       <c r="H196" s="1" t="n">
@@ -9708,44 +9744,38 @@
       <c r="J196" s="1" t="n"/>
       <c r="K196" s="1" t="n"/>
       <c r="L196" s="1" t="n"/>
-      <c r="M196" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N196" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O196" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M196" s="1" t="n"/>
+      <c r="N196" s="1" t="n"/>
+      <c r="O196" s="1" t="n"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>14015311000006110</t>
+          <t>5056471000006118</t>
         </is>
       </c>
       <c r="B197" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>^ESCT1401531</t>
+          <t>^ESCTAC505647</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>16891151000119103</t>
+          <t>233844002</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>3778765010</t>
+          <t>350378010</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Coronary artery disease due to type 2 diabetes mellitus</t>
+          <t>Accelerated coronary artery disease in transplanted heart</t>
         </is>
       </c>
       <c r="H197" s="1" t="n">
@@ -9764,31 +9794,31 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>4775981000006112</t>
+          <t>3458791000006114</t>
         </is>
       </c>
       <c r="B198" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>^ESCTCA477598</t>
+          <t>^ESCTAN345879</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>194828000</t>
+          <t>59021001</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>299756015</t>
+          <t>98088014</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Cardiac angina</t>
+          <t>Anginal chest pain at rest</t>
         </is>
       </c>
       <c r="H198" s="1" t="n">
@@ -9811,31 +9841,35 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4776021000006118</t>
+          <t>1900601000006111</t>
         </is>
       </c>
       <c r="B199" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>^ESCTIS477602</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>2Ba11</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2Ba1100</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>194828000</t>
+          <t>914891000000100</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>299761018</t>
+          <t>2350711000000114</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Ischemic heart disease - angina</t>
+          <t>Surveillance of Cerebral Palsy in Europe classification - predominant pattern B.2 - sequelae of intraventricular haemorrhage or periventricular infarction</t>
         </is>
       </c>
       <c r="H199" s="1" t="n">
@@ -9847,18 +9881,14 @@
       <c r="J199" s="1" t="n"/>
       <c r="K199" s="1" t="n"/>
       <c r="L199" s="1" t="n"/>
-      <c r="M199" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M199" s="1" t="n"/>
       <c r="N199" s="1" t="n"/>
-      <c r="O199" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O199" s="1" t="n"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>5056261000006112</t>
+          <t>14179491000006111</t>
         </is>
       </c>
       <c r="B200" s="1" t="n">
@@ -9866,44 +9896,42 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>^ESCTAS505626</t>
+          <t>^ESCT1417949</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>233823002</t>
+          <t>15960341000119104</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>350356015</t>
+          <t>3991458017</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Asymptomatic ischaemia</t>
+          <t>Unstable angina due to arteriosclerosis of coronary artery bypass graft of transplanted heart</t>
         </is>
       </c>
       <c r="H200" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I200" s="1" t="n"/>
+      <c r="I200" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="J200" s="1" t="n"/>
       <c r="K200" s="1" t="n"/>
       <c r="L200" s="1" t="n"/>
-      <c r="M200" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M200" s="1" t="n"/>
       <c r="N200" s="1" t="n"/>
-      <c r="O200" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O200" s="1" t="n"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>6864791000006113</t>
+          <t>12125971000006114</t>
         </is>
       </c>
       <c r="B201" s="1" t="n">
@@ -9911,36 +9939,40 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>^ESCTMY686479</t>
+          <t>^ESCT1212597</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>414795007</t>
+          <t>15960661000119107</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2534665017</t>
+          <t>3645129018</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Myocardial ischemia</t>
+          <t>Unstable angina co-occurrent and due to arteriosclerosis of coronary artery bypass graft</t>
         </is>
       </c>
       <c r="H201" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I201" s="1" t="n"/>
+      <c r="I201" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="J201" s="1" t="n"/>
       <c r="K201" s="1" t="n"/>
       <c r="L201" s="1" t="n"/>
       <c r="M201" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="N201" s="1" t="n"/>
+      <c r="N201" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="O201" s="1" t="n">
         <v>1</v>
       </c>
@@ -9948,7 +9980,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>7087601000006118</t>
+          <t>14015311000006110</t>
         </is>
       </c>
       <c r="B202" s="1" t="n">
@@ -9956,23 +9988,23 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>^ESCTHI708760</t>
+          <t>^ESCT1401531</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>428375006</t>
+          <t>16891151000119103</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2695581010</t>
+          <t>3778765010</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>History of coronary artery disease with stent placement</t>
+          <t>Coronary artery disease due to type 2 diabetes mellitus</t>
         </is>
       </c>
       <c r="H202" s="1" t="n">
@@ -9991,7 +10023,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>14194711000006117</t>
+          <t>4775981000006112</t>
         </is>
       </c>
       <c r="B203" s="1" t="n">
@@ -9999,66 +10031,70 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>^ESCT1419471</t>
+          <t>^ESCTCA477598</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>726499301000119105</t>
+          <t>194828000</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>4030227013</t>
+          <t>299756015</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Type 1 myocardial infarction</t>
+          <t>Cardiac angina</t>
         </is>
       </c>
       <c r="H203" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I203" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J203" s="1" t="n"/>
       <c r="K203" s="1" t="n"/>
       <c r="L203" s="1" t="n"/>
-      <c r="M203" s="1" t="n"/>
+      <c r="M203" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N203" s="1" t="n"/>
-      <c r="O203" s="1" t="n"/>
+      <c r="O203" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>9868481000006117</t>
+          <t>4776021000006118</t>
         </is>
       </c>
       <c r="B204" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>^ESCTAN986848</t>
+          <t>^ESCTIS477602</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>15960141000119102</t>
+          <t>194828000</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>3323422017</t>
+          <t>299761018</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Angina co-occurrent and due to coronary arteriosclerosis</t>
+          <t>Ischemic heart disease - angina</t>
         </is>
       </c>
       <c r="H204" s="1" t="n">
@@ -10081,38 +10117,38 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>12125951000006116</t>
+          <t>5056261000006112</t>
         </is>
       </c>
       <c r="B205" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>^ESCT1212595</t>
+          <t>^ESCTAS505626</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>15960581000119102</t>
+          <t>233823002</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>3645095017</t>
+          <t>350356015</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Arteriosclerosis of autologous vein coronary artery bypass graft with angina</t>
+          <t>Asymptomatic ischaemia</t>
         </is>
       </c>
       <c r="H205" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I205" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J205" s="1" t="n"/>
       <c r="K205" s="1" t="n"/>
@@ -10128,31 +10164,31 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>4783961000006114</t>
+          <t>6864791000006113</t>
         </is>
       </c>
       <c r="B206" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>^ESCTLU478396</t>
+          <t>^ESCTMY686479</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>196542004</t>
+          <t>414795007</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2838071016</t>
+          <t>2534665017</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Ludwig angina</t>
+          <t>Myocardial ischemia</t>
         </is>
       </c>
       <c r="H206" s="1" t="n">
@@ -10164,38 +10200,42 @@
       <c r="J206" s="1" t="n"/>
       <c r="K206" s="1" t="n"/>
       <c r="L206" s="1" t="n"/>
-      <c r="M206" s="1" t="n"/>
+      <c r="M206" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N206" s="1" t="n"/>
-      <c r="O206" s="1" t="n"/>
+      <c r="O206" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>5149551000006110</t>
+          <t>7087601000006118</t>
         </is>
       </c>
       <c r="B207" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>^ESCTSY514955</t>
+          <t>^ESCTHI708760</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>240567009</t>
+          <t>428375006</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>360348016</t>
+          <t>2695581010</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Syphilitic coronary artery disease</t>
+          <t>History of coronary artery disease with stent placement</t>
         </is>
       </c>
       <c r="H207" s="1" t="n">
@@ -10214,7 +10254,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>5974561000006110</t>
+          <t>9868481000006117</t>
         </is>
       </c>
       <c r="B208" s="1" t="n">
@@ -10222,23 +10262,23 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>^ESCTHI597456</t>
+          <t>^ESCTAN986848</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
-          <t>308068007</t>
+          <t>15960141000119102</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2986970011</t>
+          <t>3323422017</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>History of treatment for ischaemic heart disease</t>
+          <t>Angina co-occurrent and due to coronary arteriosclerosis</t>
         </is>
       </c>
       <c r="H208" s="1" t="n">
@@ -10250,14 +10290,18 @@
       <c r="J208" s="1" t="n"/>
       <c r="K208" s="1" t="n"/>
       <c r="L208" s="1" t="n"/>
-      <c r="M208" s="1" t="n"/>
+      <c r="M208" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N208" s="1" t="n"/>
-      <c r="O208" s="1" t="n"/>
+      <c r="O208" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>6060001000006112</t>
+          <t>12125951000006116</t>
         </is>
       </c>
       <c r="B209" s="1" t="n">
@@ -10265,23 +10309,23 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>^ESCTPR606000</t>
+          <t>^ESCT1212595</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
-          <t>315610002</t>
+          <t>15960581000119102</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>460128016</t>
+          <t>3645095017</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Primary prevention of ischemic heart disease</t>
+          <t>Arteriosclerosis of autologous vein coronary artery bypass graft with angina</t>
         </is>
       </c>
       <c r="H209" s="1" t="n">
@@ -10293,14 +10337,18 @@
       <c r="J209" s="1" t="n"/>
       <c r="K209" s="1" t="n"/>
       <c r="L209" s="1" t="n"/>
-      <c r="M209" s="1" t="n"/>
+      <c r="M209" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="N209" s="1" t="n"/>
-      <c r="O209" s="1" t="n"/>
+      <c r="O209" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2571531000006110</t>
+          <t>4783961000006114</t>
         </is>
       </c>
       <c r="B210" s="1" t="n">
@@ -10308,54 +10356,42 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>^ESCTIN257153</t>
+          <t>^ESCTLU478396</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
-          <t>4557003</t>
+          <t>196542004</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>7846012</t>
+          <t>2838071016</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Intermediate coronary syndrome</t>
+          <t>Ludwig angina</t>
         </is>
       </c>
       <c r="H210" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I210" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J210" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K210" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L210" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="M210" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N210" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O210" s="1" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J210" s="1" t="n"/>
+      <c r="K210" s="1" t="n"/>
+      <c r="L210" s="1" t="n"/>
+      <c r="M210" s="1" t="n"/>
+      <c r="N210" s="1" t="n"/>
+      <c r="O210" s="1" t="n"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>8021731000006112</t>
+          <t>5149551000006110</t>
         </is>
       </c>
       <c r="B211" s="1" t="n">
@@ -10363,23 +10399,23 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>^ESCTTR802173</t>
+          <t>^ESCTSY514955</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
-          <t>69051000119104</t>
+          <t>240567009</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2972520010</t>
+          <t>360348016</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Treadmill stress test negative for angina pectoris</t>
+          <t>Syphilitic coronary artery disease</t>
         </is>
       </c>
       <c r="H211" s="1" t="n">
@@ -10398,7 +10434,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3920001000006119</t>
+          <t>5974561000006110</t>
         </is>
       </c>
       <c r="B212" s="1" t="n">
@@ -10406,23 +10442,23 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>^ESCTVA392000</t>
+          <t>^ESCTHI597456</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>87343002</t>
+          <t>308068007</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>144819018</t>
+          <t>2986970011</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Variant angina pectoris</t>
+          <t>History of treatment for ischaemic heart disease</t>
         </is>
       </c>
       <c r="H212" s="1" t="n">
@@ -10434,18 +10470,14 @@
       <c r="J212" s="1" t="n"/>
       <c r="K212" s="1" t="n"/>
       <c r="L212" s="1" t="n"/>
-      <c r="M212" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M212" s="1" t="n"/>
       <c r="N212" s="1" t="n"/>
-      <c r="O212" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="O212" s="1" t="n"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>3951991000006119</t>
+          <t>6060001000006112</t>
         </is>
       </c>
       <c r="B213" s="1" t="n">
@@ -10453,23 +10485,23 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>^ESCTAN395199</t>
+          <t>^ESCTPR606000</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
-          <t>89323001</t>
+          <t>315610002</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>148118017</t>
+          <t>460128016</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Angina, class IV</t>
+          <t>Primary prevention of ischemic heart disease</t>
         </is>
       </c>
       <c r="H213" s="1" t="n">
@@ -10481,11 +10513,199 @@
       <c r="J213" s="1" t="n"/>
       <c r="K213" s="1" t="n"/>
       <c r="L213" s="1" t="n"/>
-      <c r="M213" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="M213" s="1" t="n"/>
       <c r="N213" s="1" t="n"/>
-      <c r="O213" s="1" t="n">
+      <c r="O213" s="1" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2571531000006110</t>
+        </is>
+      </c>
+      <c r="B214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>^ESCTIN257153</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>4557003</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>7846012</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Intermediate coronary syndrome</t>
+        </is>
+      </c>
+      <c r="H214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N214" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O214" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>8021731000006112</t>
+        </is>
+      </c>
+      <c r="B215" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>^ESCTTR802173</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>69051000119104</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2972520010</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Treadmill stress test negative for angina pectoris</t>
+        </is>
+      </c>
+      <c r="H215" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" s="1" t="n"/>
+      <c r="K215" s="1" t="n"/>
+      <c r="L215" s="1" t="n"/>
+      <c r="M215" s="1" t="n"/>
+      <c r="N215" s="1" t="n"/>
+      <c r="O215" s="1" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>3920001000006119</t>
+        </is>
+      </c>
+      <c r="B216" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>^ESCTVA392000</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>87343002</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>144819018</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Variant angina pectoris</t>
+        </is>
+      </c>
+      <c r="H216" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I216" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" s="1" t="n"/>
+      <c r="K216" s="1" t="n"/>
+      <c r="L216" s="1" t="n"/>
+      <c r="M216" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N216" s="1" t="n"/>
+      <c r="O216" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>3951991000006119</t>
+        </is>
+      </c>
+      <c r="B217" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>^ESCTAN395199</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>89323001</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>148118017</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Angina, class IV</t>
+        </is>
+      </c>
+      <c r="H217" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I217" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" s="1" t="n"/>
+      <c r="K217" s="1" t="n"/>
+      <c r="L217" s="1" t="n"/>
+      <c r="M217" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N217" s="1" t="n"/>
+      <c r="O217" s="1" t="n">
         <v>1</v>
       </c>
     </row>

--- a/codelists/ischaemic_heart_disease_raw.xlsx
+++ b/codelists/ischaemic_heart_disease_raw.xlsx
@@ -6319,7 +6319,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>299804015</t>
+          <t>299800012</t>
         </is>
       </c>
       <c r="B123" s="1" t="n">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>G34yz</t>
+          <t>G34y</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>G34yz00</t>
+          <t>G34y.00</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Other specified chronic ischaemic heart disease NOS</t>
+          <t>Other specified chronic ischaemic heart disease</t>
         </is>
       </c>
       <c r="H123" s="1" t="n">
@@ -6370,7 +6370,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>299800012</t>
+          <t>299804015</t>
         </is>
       </c>
       <c r="B124" s="1" t="n">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>G34y</t>
+          <t>G34yz</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>G34y.00</t>
+          <t>G34yz00</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Other specified chronic ischaemic heart disease</t>
+          <t>Other specified chronic ischaemic heart disease NOS</t>
         </is>
       </c>
       <c r="H124" s="1" t="n">
@@ -6656,7 +6656,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>6860251000006115</t>
+          <t>299750014</t>
         </is>
       </c>
       <c r="B130" s="1" t="n">
@@ -6664,10 +6664,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>^ESCTIS686025</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>G31yz</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>G31yz00</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>414545008</t>
@@ -6680,7 +6684,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ischemic heart disease</t>
+          <t>Other acute and subacute ischaemic heart disease NOS</t>
         </is>
       </c>
       <c r="H130" s="1" t="n">
@@ -6703,7 +6707,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>299750014</t>
+          <t>6860251000006115</t>
         </is>
       </c>
       <c r="B131" s="1" t="n">
@@ -6711,14 +6715,10 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>G31yz</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>G31yz00</t>
-        </is>
-      </c>
+          <t>^ESCTIS686025</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>414545008</t>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Other acute and subacute ischaemic heart disease NOS</t>
+          <t>Ischemic heart disease</t>
         </is>
       </c>
       <c r="H131" s="1" t="n">
